--- a/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/дв 20,10,26 мррсч ост сыр.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты Останкино СЫРЫ/дв 20,10,26 мррсч ост сыр.xlsx
@@ -1,29 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино СЫРЫ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\в бланки заводов\Останкино СЫР\OrderCheeseInForm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2775D79-B164-4E8D-84D1-8073AF12E247}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D7831F9-E701-44B5-BDF2-B987C5AD1813}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="заказ" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$Y$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$Z$51</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="89">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -71,9 +80,6 @@
   </si>
   <si>
     <t>ср нов</t>
-  </si>
-  <si>
-    <t>расчет</t>
   </si>
   <si>
     <t>кон ост</t>
@@ -334,13 +340,22 @@
     </r>
   </si>
   <si>
-    <t>предзаказ</t>
-  </si>
-  <si>
     <t>масло</t>
   </si>
   <si>
     <t>02,11,</t>
+  </si>
+  <si>
+    <t>итого1</t>
+  </si>
+  <si>
+    <t>заказ</t>
+  </si>
+  <si>
+    <t>26,10,</t>
+  </si>
+  <si>
+    <t>02,11,масло</t>
   </si>
 </sst>
 </file>
@@ -769,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AW499"/>
+  <dimension ref="A1:AX499"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
@@ -782,15 +797,15 @@
     <col min="10" max="10" width="1" customWidth="1"/>
     <col min="11" max="12" width="7" customWidth="1"/>
     <col min="13" max="14" width="0.28515625" customWidth="1"/>
-    <col min="15" max="18" width="7" customWidth="1"/>
-    <col min="19" max="20" width="5" customWidth="1"/>
-    <col min="21" max="23" width="6" customWidth="1"/>
-    <col min="24" max="24" width="57.7109375" customWidth="1"/>
-    <col min="25" max="25" width="7" customWidth="1"/>
-    <col min="26" max="49" width="8" customWidth="1"/>
+    <col min="15" max="19" width="7" customWidth="1"/>
+    <col min="20" max="21" width="5" customWidth="1"/>
+    <col min="22" max="24" width="6" customWidth="1"/>
+    <col min="25" max="25" width="57.7109375" customWidth="1"/>
+    <col min="26" max="27" width="7" customWidth="1"/>
+    <col min="28" max="50" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -840,8 +855,9 @@
       <c r="AU1" s="1"/>
       <c r="AV1" s="1"/>
       <c r="AW1" s="1"/>
-    </row>
-    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX1" s="1"/>
+    </row>
+    <row r="2" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
@@ -859,10 +875,10 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
-      <c r="R2" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="S2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
@@ -870,7 +886,9 @@
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
-      <c r="AA2" s="1"/>
+      <c r="AA2" s="1" t="s">
+        <v>84</v>
+      </c>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
@@ -893,8 +911,9 @@
       <c r="AU2" s="1"/>
       <c r="AV2" s="1"/>
       <c r="AW2" s="1"/>
-    </row>
-    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX2" s="1"/>
+    </row>
+    <row r="3" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -944,34 +963,38 @@
         <v>15</v>
       </c>
       <c r="Q3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="R3" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="S3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="W3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="V3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="X3" s="2" t="s">
+      <c r="Z3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="Y3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
+      <c r="AA3" s="2" t="s">
+        <v>20</v>
+      </c>
       <c r="AB3" s="1"/>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
@@ -994,8 +1017,9 @@
       <c r="AU3" s="1"/>
       <c r="AV3" s="1"/>
       <c r="AW3" s="1"/>
-    </row>
-    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX3" s="1"/>
+    </row>
+    <row r="4" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1011,30 +1035,34 @@
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
       <c r="O4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>22</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>23</v>
       </c>
       <c r="Q4" s="1"/>
       <c r="R4" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="S4" s="1"/>
+        <v>87</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="T4" s="1"/>
-      <c r="U4" s="1" t="s">
+      <c r="U4" s="1"/>
+      <c r="V4" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="W4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
-      <c r="AA4" s="1"/>
+      <c r="AA4" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="AB4" s="1"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
@@ -1057,8 +1085,9 @@
       <c r="AU4" s="1"/>
       <c r="AV4" s="1"/>
       <c r="AW4" s="1"/>
-    </row>
-    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX4" s="1"/>
+    </row>
+    <row r="5" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1076,7 +1105,7 @@
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="4">
-        <f t="shared" ref="K5:R5" si="0">SUM(K6:K499)</f>
+        <f t="shared" ref="K5:S5" si="0">SUM(K6:K499)</f>
         <v>1304</v>
       </c>
       <c r="L5" s="4">
@@ -1105,29 +1134,35 @@
       </c>
       <c r="R5" s="4">
         <f t="shared" si="0"/>
+        <v>557</v>
+      </c>
+      <c r="S5" s="4">
+        <f t="shared" si="0"/>
         <v>130</v>
       </c>
-      <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="4">
-        <f>SUM(U6:U499)</f>
-        <v>153.3888</v>
-      </c>
+      <c r="U5" s="1"/>
       <c r="V5" s="4">
         <f>SUM(V6:V499)</f>
-        <v>63.6</v>
+        <v>153.3888</v>
       </c>
       <c r="W5" s="4">
         <f>SUM(W6:W499)</f>
+        <v>63.6</v>
+      </c>
+      <c r="X5" s="4">
+        <f>SUM(X6:X499)</f>
         <v>40.945999999999998</v>
       </c>
-      <c r="X5" s="1"/>
-      <c r="Y5" s="4">
-        <f>SUM(Y6:Y499)</f>
+      <c r="Y5" s="1"/>
+      <c r="Z5" s="4">
+        <f>SUM(Z6:Z499)</f>
         <v>74.925600000000003</v>
       </c>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
+      <c r="AA5" s="4">
+        <f>SUM(AA6:AA499)</f>
+        <v>23.4</v>
+      </c>
       <c r="AB5" s="1"/>
       <c r="AC5" s="1"/>
       <c r="AD5" s="1"/>
@@ -1150,13 +1185,14 @@
       <c r="AU5" s="1"/>
       <c r="AV5" s="1"/>
       <c r="AW5" s="1"/>
-    </row>
-    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX5" s="1"/>
+    </row>
+    <row r="6" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
@@ -1188,32 +1224,35 @@
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
-      <c r="S6" s="1" t="e">
+      <c r="S6" s="5"/>
+      <c r="T6" s="1" t="e">
         <f>(F6+O6+Q6)/P6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T6" s="1" t="e">
+      <c r="U6" s="1" t="e">
         <f>(F6+O6)/P6</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="U6" s="1">
-        <v>0</v>
-      </c>
       <c r="V6" s="1">
         <v>0</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
       </c>
-      <c r="X6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y6" s="1">
-        <f t="shared" ref="Y6:Y51" si="3">G6*Q6</f>
+      <c r="X6" s="1">
         <v>0</v>
       </c>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
+      <c r="Y6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" ref="Z6:Z51" si="3">G6*Q6</f>
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
+        <f>G6*S6</f>
+        <v>0</v>
+      </c>
       <c r="AB6" s="1"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
@@ -1236,13 +1275,14 @@
       <c r="AU6" s="1"/>
       <c r="AV6" s="1"/>
       <c r="AW6" s="1"/>
-    </row>
-    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX6" s="1"/>
+    </row>
+    <row r="7" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="1">
         <v>72</v>
@@ -1280,16 +1320,14 @@
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
-      <c r="S7" s="1">
-        <f t="shared" ref="S7:S51" si="4">(F7+O7+Q7)/P7</f>
+      <c r="S7" s="5"/>
+      <c r="T7" s="1">
+        <f t="shared" ref="T7:T51" si="4">(F7+O7+Q7)/P7</f>
         <v>235</v>
       </c>
-      <c r="T7" s="1">
-        <f t="shared" ref="T7:T51" si="5">(F7+O7)/P7</f>
+      <c r="U7" s="1">
+        <f t="shared" ref="U7:U51" si="5">(F7+O7)/P7</f>
         <v>235</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
       </c>
       <c r="V7" s="1">
         <v>0</v>
@@ -1297,15 +1335,20 @@
       <c r="W7" s="1">
         <v>0</v>
       </c>
-      <c r="X7" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y7" s="1">
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z7" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z7" s="1"/>
-      <c r="AA7" s="1"/>
+      <c r="AA7" s="1">
+        <f t="shared" ref="AA7:AA51" si="6">G7*S7</f>
+        <v>0</v>
+      </c>
       <c r="AB7" s="1"/>
       <c r="AC7" s="1"/>
       <c r="AD7" s="1"/>
@@ -1328,13 +1371,14 @@
       <c r="AU7" s="1"/>
       <c r="AV7" s="1"/>
       <c r="AW7" s="1"/>
-    </row>
-    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX7" s="1"/>
+    </row>
+    <row r="8" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
@@ -1372,32 +1416,35 @@
       </c>
       <c r="Q8" s="5"/>
       <c r="R8" s="5"/>
-      <c r="S8" s="1">
+      <c r="S8" s="5"/>
+      <c r="T8" s="1">
         <f t="shared" si="4"/>
         <v>115</v>
       </c>
-      <c r="T8" s="1">
+      <c r="U8" s="1">
         <f t="shared" si="5"/>
         <v>115</v>
       </c>
-      <c r="U8" s="1">
-        <v>0</v>
-      </c>
       <c r="V8" s="1">
         <v>0</v>
       </c>
       <c r="W8" s="1">
         <v>0</v>
       </c>
-      <c r="X8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Y8" s="1">
+      <c r="X8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z8" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
+      <c r="AA8" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
@@ -1420,13 +1467,14 @@
       <c r="AU8" s="1"/>
       <c r="AV8" s="1"/>
       <c r="AW8" s="1"/>
-    </row>
-    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX8" s="1"/>
+    </row>
+    <row r="9" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>32</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>33</v>
       </c>
       <c r="C9" s="1">
         <v>74.682000000000002</v>
@@ -1447,7 +1495,7 @@
         <v>120</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J9" s="1"/>
       <c r="K9" s="1">
@@ -1468,32 +1516,35 @@
       </c>
       <c r="Q9" s="5"/>
       <c r="R9" s="5"/>
-      <c r="S9" s="1">
+      <c r="S9" s="5"/>
+      <c r="T9" s="1">
         <f t="shared" si="4"/>
         <v>912.5262237762239</v>
       </c>
-      <c r="T9" s="1">
+      <c r="U9" s="1">
         <f t="shared" si="5"/>
         <v>912.5262237762239</v>
       </c>
-      <c r="U9" s="1">
+      <c r="V9" s="1">
         <v>4.0987999999999998</v>
-      </c>
-      <c r="V9" s="1">
-        <v>0</v>
       </c>
       <c r="W9" s="1">
         <v>0</v>
       </c>
-      <c r="X9" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y9" s="1">
+      <c r="X9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z9" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z9" s="1"/>
-      <c r="AA9" s="1"/>
+      <c r="AA9" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB9" s="1"/>
       <c r="AC9" s="1"/>
       <c r="AD9" s="1"/>
@@ -1516,13 +1567,14 @@
       <c r="AU9" s="1"/>
       <c r="AV9" s="1"/>
       <c r="AW9" s="1"/>
-    </row>
-    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX9" s="1"/>
+    </row>
+    <row r="10" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1">
         <v>29.931999999999999</v>
@@ -1543,7 +1595,7 @@
         <v>180</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1">
@@ -1564,32 +1616,35 @@
       </c>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
-      <c r="S10" s="1">
+      <c r="S10" s="5"/>
+      <c r="T10" s="1">
         <f t="shared" si="4"/>
         <v>61.833616298811549</v>
       </c>
-      <c r="T10" s="1">
+      <c r="U10" s="1">
         <f t="shared" si="5"/>
         <v>61.833616298811549</v>
       </c>
-      <c r="U10" s="1">
-        <v>0</v>
-      </c>
       <c r="V10" s="1">
         <v>0</v>
       </c>
       <c r="W10" s="1">
         <v>0</v>
       </c>
-      <c r="X10" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y10" s="1">
+      <c r="X10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z10" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z10" s="1"/>
-      <c r="AA10" s="1"/>
+      <c r="AA10" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB10" s="1"/>
       <c r="AC10" s="1"/>
       <c r="AD10" s="1"/>
@@ -1612,13 +1667,14 @@
       <c r="AU10" s="1"/>
       <c r="AV10" s="1"/>
       <c r="AW10" s="1"/>
-    </row>
-    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX10" s="1"/>
+    </row>
+    <row r="11" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="1">
         <v>140</v>
@@ -1635,7 +1691,7 @@
         <v>180</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J11" s="1"/>
       <c r="K11" s="1">
@@ -1654,32 +1710,35 @@
       </c>
       <c r="Q11" s="5"/>
       <c r="R11" s="5"/>
-      <c r="S11" s="1" t="e">
+      <c r="S11" s="5"/>
+      <c r="T11" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T11" s="1" t="e">
+      <c r="U11" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U11" s="1">
-        <v>1</v>
-      </c>
       <c r="V11" s="1">
         <v>1</v>
       </c>
       <c r="W11" s="1">
+        <v>1</v>
+      </c>
+      <c r="X11" s="1">
         <v>0.4</v>
       </c>
-      <c r="X11" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="Y11" s="1">
+      <c r="Y11" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z11" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="1"/>
-      <c r="AA11" s="1"/>
+      <c r="AA11" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB11" s="1"/>
       <c r="AC11" s="1"/>
       <c r="AD11" s="1"/>
@@ -1702,13 +1761,14 @@
       <c r="AU11" s="1"/>
       <c r="AV11" s="1"/>
       <c r="AW11" s="1"/>
-    </row>
-    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX11" s="1"/>
+    </row>
+    <row r="12" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C12" s="1">
         <v>90</v>
@@ -1729,7 +1789,7 @@
         <v>180</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J12" s="1"/>
       <c r="K12" s="1">
@@ -1750,32 +1810,35 @@
       </c>
       <c r="Q12" s="5"/>
       <c r="R12" s="5"/>
-      <c r="S12" s="1">
+      <c r="S12" s="5"/>
+      <c r="T12" s="1">
         <f t="shared" si="4"/>
         <v>25.384615384615387</v>
       </c>
-      <c r="T12" s="1">
+      <c r="U12" s="1">
         <f t="shared" si="5"/>
         <v>25.384615384615387</v>
       </c>
-      <c r="U12" s="1">
+      <c r="V12" s="1">
         <v>2.8</v>
       </c>
-      <c r="V12" s="1">
+      <c r="W12" s="1">
         <v>4.5999999999999996</v>
       </c>
-      <c r="W12" s="1">
+      <c r="X12" s="1">
         <v>6</v>
       </c>
-      <c r="X12" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y12" s="1">
+      <c r="Y12" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z12" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="1"/>
-      <c r="AA12" s="1"/>
+      <c r="AA12" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB12" s="1"/>
       <c r="AC12" s="1"/>
       <c r="AD12" s="1"/>
@@ -1798,13 +1861,14 @@
       <c r="AU12" s="1"/>
       <c r="AV12" s="1"/>
       <c r="AW12" s="1"/>
-    </row>
-    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX12" s="1"/>
+    </row>
+    <row r="13" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C13" s="1">
         <v>60</v>
@@ -1825,7 +1889,7 @@
         <v>180</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J13" s="1"/>
       <c r="K13" s="1">
@@ -1846,32 +1910,35 @@
       </c>
       <c r="Q13" s="5"/>
       <c r="R13" s="5"/>
-      <c r="S13" s="1">
+      <c r="S13" s="5"/>
+      <c r="T13" s="1">
         <f t="shared" si="4"/>
         <v>353.33333333333337</v>
       </c>
-      <c r="T13" s="1">
+      <c r="U13" s="1">
         <f t="shared" si="5"/>
         <v>353.33333333333337</v>
       </c>
-      <c r="U13" s="1">
+      <c r="V13" s="1">
         <v>6</v>
       </c>
-      <c r="V13" s="1">
+      <c r="W13" s="1">
         <v>1</v>
       </c>
-      <c r="W13" s="1">
+      <c r="X13" s="1">
         <v>3.6</v>
       </c>
-      <c r="X13" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y13" s="1">
+      <c r="Y13" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z13" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z13" s="1"/>
-      <c r="AA13" s="1"/>
+      <c r="AA13" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB13" s="1"/>
       <c r="AC13" s="1"/>
       <c r="AD13" s="1"/>
@@ -1894,13 +1961,14 @@
       <c r="AU13" s="1"/>
       <c r="AV13" s="1"/>
       <c r="AW13" s="1"/>
-    </row>
-    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX13" s="1"/>
+    </row>
+    <row r="14" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C14" s="1">
         <v>148</v>
@@ -1921,7 +1989,7 @@
         <v>180</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1">
@@ -1942,32 +2010,35 @@
       </c>
       <c r="Q14" s="5"/>
       <c r="R14" s="5"/>
-      <c r="S14" s="1">
+      <c r="S14" s="5"/>
+      <c r="T14" s="1">
         <f t="shared" si="4"/>
         <v>34.722222222222221</v>
       </c>
-      <c r="T14" s="1">
+      <c r="U14" s="1">
         <f t="shared" si="5"/>
         <v>34.722222222222221</v>
       </c>
-      <c r="U14" s="1">
+      <c r="V14" s="1">
         <v>5.6</v>
       </c>
-      <c r="V14" s="1">
+      <c r="W14" s="1">
         <v>0.8</v>
       </c>
-      <c r="W14" s="1">
+      <c r="X14" s="1">
         <v>2</v>
       </c>
-      <c r="X14" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y14" s="1">
+      <c r="Y14" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z14" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z14" s="1"/>
-      <c r="AA14" s="1"/>
+      <c r="AA14" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
@@ -1990,13 +2061,14 @@
       <c r="AU14" s="1"/>
       <c r="AV14" s="1"/>
       <c r="AW14" s="1"/>
-    </row>
-    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX14" s="1"/>
+    </row>
+    <row r="15" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C15" s="1">
         <v>98</v>
@@ -2017,7 +2089,7 @@
         <v>180</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J15" s="1"/>
       <c r="K15" s="1">
@@ -2038,30 +2110,33 @@
       </c>
       <c r="Q15" s="5"/>
       <c r="R15" s="5"/>
-      <c r="S15" s="1">
+      <c r="S15" s="5"/>
+      <c r="T15" s="1">
         <f t="shared" si="4"/>
         <v>19.069767441860467</v>
       </c>
-      <c r="T15" s="1">
+      <c r="U15" s="1">
         <f t="shared" si="5"/>
         <v>19.069767441860467</v>
       </c>
-      <c r="U15" s="1">
+      <c r="V15" s="1">
         <v>7.8</v>
-      </c>
-      <c r="V15" s="1">
-        <v>0</v>
       </c>
       <c r="W15" s="1">
         <v>0</v>
       </c>
-      <c r="X15" s="1"/>
-      <c r="Y15" s="1">
+      <c r="X15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z15" s="1"/>
-      <c r="AA15" s="1"/>
+      <c r="AA15" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB15" s="1"/>
       <c r="AC15" s="1"/>
       <c r="AD15" s="1"/>
@@ -2084,13 +2159,14 @@
       <c r="AU15" s="1"/>
       <c r="AV15" s="1"/>
       <c r="AW15" s="1"/>
-    </row>
-    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX15" s="1"/>
+    </row>
+    <row r="16" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1">
         <v>14</v>
@@ -2128,32 +2204,35 @@
       </c>
       <c r="Q16" s="5"/>
       <c r="R16" s="5"/>
-      <c r="S16" s="1">
+      <c r="S16" s="5"/>
+      <c r="T16" s="1">
         <f t="shared" si="4"/>
         <v>68.75</v>
       </c>
-      <c r="T16" s="1">
+      <c r="U16" s="1">
         <f t="shared" si="5"/>
         <v>68.75</v>
       </c>
-      <c r="U16" s="1">
+      <c r="V16" s="1">
         <v>0.4</v>
-      </c>
-      <c r="V16" s="1">
-        <v>0</v>
       </c>
       <c r="W16" s="1">
         <v>0</v>
       </c>
-      <c r="X16" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y16" s="1">
+      <c r="X16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z16" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z16" s="1"/>
-      <c r="AA16" s="1"/>
+      <c r="AA16" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB16" s="1"/>
       <c r="AC16" s="1"/>
       <c r="AD16" s="1"/>
@@ -2176,13 +2255,14 @@
       <c r="AU16" s="1"/>
       <c r="AV16" s="1"/>
       <c r="AW16" s="1"/>
-    </row>
-    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX16" s="1"/>
+    </row>
+    <row r="17" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C17" s="1">
         <v>10</v>
@@ -2203,7 +2283,7 @@
         <v>270</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J17" s="1"/>
       <c r="K17" s="1">
@@ -2221,34 +2301,40 @@
         <v>3</v>
       </c>
       <c r="Q17" s="5">
-        <f t="shared" ref="Q17:Q49" si="6">17*P17-O17-F17</f>
+        <f t="shared" ref="Q17:Q49" si="7">17*P17-O17-F17</f>
         <v>12</v>
       </c>
-      <c r="R17" s="5"/>
-      <c r="S17" s="1">
+      <c r="R17" s="5">
+        <f>VLOOKUP(A17,заказ!A:B,2,0)</f>
+        <v>16</v>
+      </c>
+      <c r="S17" s="5"/>
+      <c r="T17" s="1">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="T17" s="1">
+      <c r="U17" s="1">
         <f t="shared" si="5"/>
         <v>13</v>
       </c>
-      <c r="U17" s="1">
+      <c r="V17" s="1">
         <v>1.2</v>
-      </c>
-      <c r="V17" s="1">
-        <v>0</v>
       </c>
       <c r="W17" s="1">
         <v>0</v>
       </c>
-      <c r="X17" s="1"/>
-      <c r="Y17" s="1">
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1">
         <f t="shared" si="3"/>
         <v>2.16</v>
       </c>
-      <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
+      <c r="AA17" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB17" s="1"/>
       <c r="AC17" s="1"/>
       <c r="AD17" s="1"/>
@@ -2271,13 +2357,14 @@
       <c r="AU17" s="1"/>
       <c r="AV17" s="1"/>
       <c r="AW17" s="1"/>
-    </row>
-    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX17" s="1"/>
+    </row>
+    <row r="18" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C18" s="1">
         <v>10</v>
@@ -2298,7 +2385,7 @@
         <v>270</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J18" s="1"/>
       <c r="K18" s="1">
@@ -2317,30 +2404,33 @@
       </c>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
-      <c r="S18" s="1">
+      <c r="S18" s="5"/>
+      <c r="T18" s="1">
         <f t="shared" si="4"/>
         <v>17.916666666666668</v>
       </c>
-      <c r="T18" s="1">
+      <c r="U18" s="1">
         <f t="shared" si="5"/>
         <v>17.916666666666668</v>
       </c>
-      <c r="U18" s="1">
+      <c r="V18" s="1">
         <v>1.2</v>
-      </c>
-      <c r="V18" s="1">
-        <v>0</v>
       </c>
       <c r="W18" s="1">
         <v>0</v>
       </c>
-      <c r="X18" s="1"/>
-      <c r="Y18" s="1">
+      <c r="X18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
+      <c r="AA18" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
@@ -2363,13 +2453,14 @@
       <c r="AU18" s="1"/>
       <c r="AV18" s="1"/>
       <c r="AW18" s="1"/>
-    </row>
-    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX18" s="1"/>
+    </row>
+    <row r="19" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" s="1"/>
       <c r="D19" s="1">
@@ -2405,30 +2496,33 @@
       </c>
       <c r="Q19" s="5"/>
       <c r="R19" s="5"/>
-      <c r="S19" s="1">
+      <c r="S19" s="5"/>
+      <c r="T19" s="1">
         <f t="shared" si="4"/>
         <v>92.5</v>
       </c>
-      <c r="T19" s="1">
+      <c r="U19" s="1">
         <f t="shared" si="5"/>
         <v>92.5</v>
       </c>
-      <c r="U19" s="1">
-        <v>0</v>
-      </c>
       <c r="V19" s="1">
         <v>0</v>
       </c>
       <c r="W19" s="1">
         <v>0</v>
       </c>
-      <c r="X19" s="1"/>
-      <c r="Y19" s="1">
+      <c r="X19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z19" s="1"/>
-      <c r="AA19" s="1"/>
+      <c r="AA19" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
@@ -2451,13 +2545,14 @@
       <c r="AU19" s="1"/>
       <c r="AV19" s="1"/>
       <c r="AW19" s="1"/>
-    </row>
-    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX19" s="1"/>
+    </row>
+    <row r="20" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C20" s="1">
         <v>451</v>
@@ -2478,7 +2573,7 @@
         <v>180</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J20" s="1"/>
       <c r="K20" s="1">
@@ -2497,32 +2592,35 @@
       </c>
       <c r="Q20" s="5"/>
       <c r="R20" s="5"/>
-      <c r="S20" s="1">
-        <f>(F20+O20+Q20+R20)/P20</f>
+      <c r="S20" s="5"/>
+      <c r="T20" s="1">
+        <f>(F20+O20+Q20+S20)/P20</f>
         <v>39.523809523809526</v>
       </c>
-      <c r="T20" s="1">
+      <c r="U20" s="1">
         <f t="shared" si="5"/>
         <v>39.523809523809526</v>
       </c>
-      <c r="U20" s="1">
+      <c r="V20" s="1">
         <v>11.2</v>
-      </c>
-      <c r="V20" s="1">
-        <v>0</v>
       </c>
       <c r="W20" s="1">
         <v>0</v>
       </c>
-      <c r="X20" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y20" s="1">
+      <c r="X20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z20" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
+      <c r="AA20" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB20" s="1"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
@@ -2545,13 +2643,14 @@
       <c r="AU20" s="1"/>
       <c r="AV20" s="1"/>
       <c r="AW20" s="1"/>
-    </row>
-    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX20" s="1"/>
+    </row>
+    <row r="21" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C21" s="1">
         <v>107</v>
@@ -2572,7 +2671,7 @@
         <v>180</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1">
@@ -2590,38 +2689,44 @@
         <v>25.2</v>
       </c>
       <c r="Q21" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>151.39999999999998</v>
       </c>
       <c r="R21" s="5">
+        <f>VLOOKUP(A21,заказ!A:B,2,0)</f>
+        <v>150</v>
+      </c>
+      <c r="S21" s="5">
         <v>130</v>
       </c>
-      <c r="S21" s="1">
-        <f>(F21+O21+Q21+R21)/P21</f>
+      <c r="T21" s="1">
+        <f>(F21+O21+Q21+S21)/P21</f>
         <v>22.158730158730158</v>
       </c>
-      <c r="T21" s="1">
+      <c r="U21" s="1">
         <f t="shared" si="5"/>
         <v>10.992063492063492</v>
       </c>
-      <c r="U21" s="1">
+      <c r="V21" s="1">
         <v>9.6</v>
-      </c>
-      <c r="V21" s="1">
-        <v>0</v>
       </c>
       <c r="W21" s="1">
         <v>0</v>
       </c>
-      <c r="X21" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y21" s="1">
+      <c r="X21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z21" s="1">
         <f t="shared" si="3"/>
         <v>27.251999999999995</v>
       </c>
-      <c r="Z21" s="1"/>
-      <c r="AA21" s="1"/>
+      <c r="AA21" s="1">
+        <f t="shared" si="6"/>
+        <v>23.4</v>
+      </c>
       <c r="AB21" s="1"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
@@ -2644,13 +2749,14 @@
       <c r="AU21" s="1"/>
       <c r="AV21" s="1"/>
       <c r="AW21" s="1"/>
-    </row>
-    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX21" s="1"/>
+    </row>
+    <row r="22" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C22" s="1">
         <v>22</v>
@@ -2671,7 +2777,7 @@
         <v>270</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J22" s="1"/>
       <c r="K22" s="1">
@@ -2690,32 +2796,35 @@
       </c>
       <c r="Q22" s="5"/>
       <c r="R22" s="5"/>
-      <c r="S22" s="1">
+      <c r="S22" s="5"/>
+      <c r="T22" s="1">
         <f t="shared" si="4"/>
         <v>20</v>
       </c>
-      <c r="T22" s="1">
+      <c r="U22" s="1">
         <f t="shared" si="5"/>
         <v>20</v>
       </c>
-      <c r="U22" s="1">
+      <c r="V22" s="1">
         <v>0.4</v>
-      </c>
-      <c r="V22" s="1">
-        <v>0</v>
       </c>
       <c r="W22" s="1">
         <v>0</v>
       </c>
-      <c r="X22" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y22" s="1">
+      <c r="X22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z22" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z22" s="1"/>
-      <c r="AA22" s="1"/>
+      <c r="AA22" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB22" s="1"/>
       <c r="AC22" s="1"/>
       <c r="AD22" s="1"/>
@@ -2738,13 +2847,14 @@
       <c r="AU22" s="1"/>
       <c r="AV22" s="1"/>
       <c r="AW22" s="1"/>
-    </row>
-    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX22" s="1"/>
+    </row>
+    <row r="23" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C23" s="1">
         <v>28</v>
@@ -2765,7 +2875,7 @@
         <v>270</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J23" s="1"/>
       <c r="K23" s="1">
@@ -2784,32 +2894,35 @@
       </c>
       <c r="Q23" s="5"/>
       <c r="R23" s="5"/>
-      <c r="S23" s="1">
+      <c r="S23" s="5"/>
+      <c r="T23" s="1">
         <f t="shared" si="4"/>
         <v>88.333333333333343</v>
       </c>
-      <c r="T23" s="1">
+      <c r="U23" s="1">
         <f t="shared" si="5"/>
         <v>88.333333333333343</v>
       </c>
-      <c r="U23" s="1">
-        <v>0</v>
-      </c>
       <c r="V23" s="1">
         <v>0</v>
       </c>
       <c r="W23" s="1">
         <v>0</v>
       </c>
-      <c r="X23" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y23" s="1">
+      <c r="X23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z23" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z23" s="1"/>
-      <c r="AA23" s="1"/>
+      <c r="AA23" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB23" s="1"/>
       <c r="AC23" s="1"/>
       <c r="AD23" s="1"/>
@@ -2832,13 +2945,14 @@
       <c r="AU23" s="1"/>
       <c r="AV23" s="1"/>
       <c r="AW23" s="1"/>
-    </row>
-    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX23" s="1"/>
+    </row>
+    <row r="24" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1">
         <v>32</v>
@@ -2855,7 +2969,7 @@
         <v>270</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
@@ -2872,32 +2986,35 @@
       </c>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
-      <c r="S24" s="1" t="e">
+      <c r="S24" s="5"/>
+      <c r="T24" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T24" s="1" t="e">
+      <c r="U24" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U24" s="1">
-        <v>0</v>
-      </c>
       <c r="V24" s="1">
         <v>0</v>
       </c>
       <c r="W24" s="1">
         <v>0</v>
       </c>
-      <c r="X24" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y24" s="1">
+      <c r="X24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z24" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z24" s="1"/>
-      <c r="AA24" s="1"/>
+      <c r="AA24" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
@@ -2920,13 +3037,14 @@
       <c r="AU24" s="1"/>
       <c r="AV24" s="1"/>
       <c r="AW24" s="1"/>
-    </row>
-    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX24" s="1"/>
+    </row>
+    <row r="25" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="1">
         <v>24</v>
@@ -2964,32 +3082,35 @@
       </c>
       <c r="Q25" s="5"/>
       <c r="R25" s="5"/>
-      <c r="S25" s="1">
+      <c r="S25" s="5"/>
+      <c r="T25" s="1">
         <f t="shared" si="4"/>
         <v>195</v>
       </c>
-      <c r="T25" s="1">
+      <c r="U25" s="1">
         <f t="shared" si="5"/>
         <v>195</v>
       </c>
-      <c r="U25" s="1">
-        <v>0</v>
-      </c>
       <c r="V25" s="1">
         <v>0</v>
       </c>
       <c r="W25" s="1">
         <v>0</v>
       </c>
-      <c r="X25" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y25" s="1">
+      <c r="X25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z25" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
+      <c r="AA25" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB25" s="1"/>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
@@ -3012,13 +3133,14 @@
       <c r="AU25" s="1"/>
       <c r="AV25" s="1"/>
       <c r="AW25" s="1"/>
-    </row>
-    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX25" s="1"/>
+    </row>
+    <row r="26" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26" s="1"/>
       <c r="D26" s="1">
@@ -3035,7 +3157,7 @@
         <v>180</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
@@ -3052,30 +3174,33 @@
       </c>
       <c r="Q26" s="5"/>
       <c r="R26" s="5"/>
-      <c r="S26" s="1" t="e">
+      <c r="S26" s="5"/>
+      <c r="T26" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T26" s="1" t="e">
+      <c r="U26" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U26" s="1">
-        <v>0</v>
-      </c>
       <c r="V26" s="1">
         <v>0</v>
       </c>
       <c r="W26" s="1">
         <v>0</v>
       </c>
-      <c r="X26" s="1"/>
-      <c r="Y26" s="1">
+      <c r="X26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="1"/>
+      <c r="Z26" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z26" s="1"/>
-      <c r="AA26" s="1"/>
+      <c r="AA26" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
       <c r="AD26" s="1"/>
@@ -3098,13 +3223,14 @@
       <c r="AU26" s="1"/>
       <c r="AV26" s="1"/>
       <c r="AW26" s="1"/>
-    </row>
-    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX26" s="1"/>
+    </row>
+    <row r="27" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="1">
         <v>19.184999999999999</v>
@@ -3125,7 +3251,7 @@
         <v>180</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J27" s="1"/>
       <c r="K27" s="1">
@@ -3144,32 +3270,35 @@
       </c>
       <c r="Q27" s="5"/>
       <c r="R27" s="5"/>
-      <c r="S27" s="1">
+      <c r="S27" s="5"/>
+      <c r="T27" s="1">
         <f t="shared" si="4"/>
         <v>85.84384858044163</v>
       </c>
-      <c r="T27" s="1">
+      <c r="U27" s="1">
         <f t="shared" si="5"/>
         <v>85.84384858044163</v>
       </c>
-      <c r="U27" s="1">
-        <v>0</v>
-      </c>
       <c r="V27" s="1">
         <v>0</v>
       </c>
       <c r="W27" s="1">
         <v>0</v>
       </c>
-      <c r="X27" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y27" s="1">
+      <c r="X27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z27" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z27" s="1"/>
-      <c r="AA27" s="1"/>
+      <c r="AA27" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
@@ -3192,13 +3321,14 @@
       <c r="AU27" s="1"/>
       <c r="AV27" s="1"/>
       <c r="AW27" s="1"/>
-    </row>
-    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX27" s="1"/>
+    </row>
+    <row r="28" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="1">
         <v>82</v>
@@ -3219,7 +3349,7 @@
         <v>150</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J28" s="1"/>
       <c r="K28" s="1">
@@ -3238,32 +3368,35 @@
       </c>
       <c r="Q28" s="5"/>
       <c r="R28" s="5"/>
-      <c r="S28" s="1">
+      <c r="S28" s="5"/>
+      <c r="T28" s="1">
         <f t="shared" si="4"/>
         <v>22.826086956521742</v>
       </c>
-      <c r="T28" s="1">
+      <c r="U28" s="1">
         <f t="shared" si="5"/>
         <v>22.826086956521742</v>
       </c>
-      <c r="U28" s="1">
+      <c r="V28" s="1">
         <v>5.2</v>
-      </c>
-      <c r="V28" s="1">
-        <v>0</v>
       </c>
       <c r="W28" s="1">
         <v>0</v>
       </c>
-      <c r="X28" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y28" s="1">
+      <c r="X28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z28" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z28" s="1"/>
-      <c r="AA28" s="1"/>
+      <c r="AA28" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
@@ -3286,13 +3419,14 @@
       <c r="AU28" s="1"/>
       <c r="AV28" s="1"/>
       <c r="AW28" s="1"/>
-    </row>
-    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX28" s="1"/>
+    </row>
+    <row r="29" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="1">
         <v>13</v>
@@ -3329,34 +3463,40 @@
         <v>4.8</v>
       </c>
       <c r="Q29" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>52.599999999999994</v>
       </c>
-      <c r="R29" s="5"/>
-      <c r="S29" s="1">
+      <c r="R29" s="5">
+        <f>VLOOKUP(A29,заказ!A:B,2,0)</f>
+        <v>56</v>
+      </c>
+      <c r="S29" s="5"/>
+      <c r="T29" s="1">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="T29" s="1">
+      <c r="U29" s="1">
         <f t="shared" si="5"/>
         <v>6.041666666666667</v>
       </c>
-      <c r="U29" s="1">
+      <c r="V29" s="1">
         <v>8.1999999999999993</v>
       </c>
-      <c r="V29" s="1">
+      <c r="W29" s="1">
         <v>12.8</v>
       </c>
-      <c r="W29" s="1">
+      <c r="X29" s="1">
         <v>3.6</v>
       </c>
-      <c r="X29" s="1"/>
-      <c r="Y29" s="1">
+      <c r="Y29" s="1"/>
+      <c r="Z29" s="1">
         <f t="shared" si="3"/>
         <v>5.26</v>
       </c>
-      <c r="Z29" s="1"/>
-      <c r="AA29" s="1"/>
+      <c r="AA29" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
@@ -3379,13 +3519,14 @@
       <c r="AU29" s="1"/>
       <c r="AV29" s="1"/>
       <c r="AW29" s="1"/>
-    </row>
-    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX29" s="1"/>
+    </row>
+    <row r="30" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" s="1">
         <v>88</v>
@@ -3424,34 +3565,40 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="Q30" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>24.600000000000023</v>
       </c>
-      <c r="R30" s="5"/>
-      <c r="S30" s="1">
+      <c r="R30" s="5">
+        <f>VLOOKUP(A30,заказ!A:B,2,0)</f>
+        <v>24</v>
+      </c>
+      <c r="S30" s="5"/>
+      <c r="T30" s="1">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="T30" s="1">
+      <c r="U30" s="1">
         <f t="shared" si="5"/>
         <v>14.204545454545453</v>
       </c>
-      <c r="U30" s="1">
+      <c r="V30" s="1">
         <v>10.199999999999999</v>
-      </c>
-      <c r="V30" s="1">
-        <v>0</v>
       </c>
       <c r="W30" s="1">
         <v>0</v>
       </c>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1">
+      <c r="X30" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="1"/>
+      <c r="Z30" s="1">
         <f t="shared" si="3"/>
         <v>2.4600000000000026</v>
       </c>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
+      <c r="AA30" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
@@ -3474,13 +3621,14 @@
       <c r="AU30" s="1"/>
       <c r="AV30" s="1"/>
       <c r="AW30" s="1"/>
-    </row>
-    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX30" s="1"/>
+    </row>
+    <row r="31" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="1">
         <v>110</v>
@@ -3517,34 +3665,40 @@
         <v>6.4</v>
       </c>
       <c r="Q31" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>27.800000000000011</v>
       </c>
-      <c r="R31" s="5"/>
-      <c r="S31" s="1">
+      <c r="R31" s="5">
+        <f>VLOOKUP(A31,заказ!A:B,2,0)</f>
+        <v>24</v>
+      </c>
+      <c r="S31" s="5"/>
+      <c r="T31" s="1">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="T31" s="1">
+      <c r="U31" s="1">
         <f t="shared" si="5"/>
         <v>12.65625</v>
       </c>
-      <c r="U31" s="1">
+      <c r="V31" s="1">
         <v>3.6</v>
-      </c>
-      <c r="V31" s="1">
-        <v>0</v>
       </c>
       <c r="W31" s="1">
         <v>0</v>
       </c>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1">
+      <c r="X31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1">
         <f t="shared" si="3"/>
         <v>2.7800000000000011</v>
       </c>
-      <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
+      <c r="AA31" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
@@ -3567,13 +3721,14 @@
       <c r="AU31" s="1"/>
       <c r="AV31" s="1"/>
       <c r="AW31" s="1"/>
-    </row>
-    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX31" s="1"/>
+    </row>
+    <row r="32" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" s="1">
         <v>58</v>
@@ -3594,7 +3749,7 @@
         <v>150</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J32" s="1"/>
       <c r="K32" s="1">
@@ -3615,32 +3770,35 @@
       </c>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
-      <c r="S32" s="1">
+      <c r="S32" s="5"/>
+      <c r="T32" s="1">
         <f t="shared" si="4"/>
         <v>64</v>
       </c>
-      <c r="T32" s="1">
+      <c r="U32" s="1">
         <f t="shared" si="5"/>
         <v>64</v>
       </c>
-      <c r="U32" s="1">
+      <c r="V32" s="1">
         <v>4.2</v>
-      </c>
-      <c r="V32" s="1">
-        <v>0</v>
       </c>
       <c r="W32" s="1">
         <v>0</v>
       </c>
-      <c r="X32" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y32" s="1">
+      <c r="X32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z32" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z32" s="1"/>
-      <c r="AA32" s="1"/>
+      <c r="AA32" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
@@ -3663,13 +3821,14 @@
       <c r="AU32" s="1"/>
       <c r="AV32" s="1"/>
       <c r="AW32" s="1"/>
-    </row>
-    <row r="33" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX32" s="1"/>
+    </row>
+    <row r="33" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33" s="1">
         <v>85</v>
@@ -3690,7 +3849,7 @@
         <v>150</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J33" s="1"/>
       <c r="K33" s="1">
@@ -3711,32 +3870,35 @@
       </c>
       <c r="Q33" s="5"/>
       <c r="R33" s="5"/>
-      <c r="S33" s="1">
+      <c r="S33" s="5"/>
+      <c r="T33" s="1">
         <f t="shared" si="4"/>
         <v>24.655172413793103</v>
       </c>
-      <c r="T33" s="1">
+      <c r="U33" s="1">
         <f t="shared" si="5"/>
         <v>24.655172413793103</v>
       </c>
-      <c r="U33" s="1">
+      <c r="V33" s="1">
         <v>15</v>
-      </c>
-      <c r="V33" s="1">
-        <v>0</v>
       </c>
       <c r="W33" s="1">
         <v>0</v>
       </c>
-      <c r="X33" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y33" s="1">
+      <c r="X33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z33" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z33" s="1"/>
-      <c r="AA33" s="1"/>
+      <c r="AA33" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
@@ -3759,13 +3921,14 @@
       <c r="AU33" s="1"/>
       <c r="AV33" s="1"/>
       <c r="AW33" s="1"/>
-    </row>
-    <row r="34" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX33" s="1"/>
+    </row>
+    <row r="34" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1">
         <v>18</v>
@@ -3786,7 +3949,7 @@
         <v>150</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1">
@@ -3807,32 +3970,35 @@
       </c>
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
-      <c r="S34" s="1">
+      <c r="S34" s="5"/>
+      <c r="T34" s="1">
         <f t="shared" si="4"/>
         <v>78.571428571428569</v>
       </c>
-      <c r="T34" s="1">
+      <c r="U34" s="1">
         <f t="shared" si="5"/>
         <v>78.571428571428569</v>
       </c>
-      <c r="U34" s="1">
+      <c r="V34" s="1">
         <v>2.4</v>
-      </c>
-      <c r="V34" s="1">
-        <v>0</v>
       </c>
       <c r="W34" s="1">
         <v>0</v>
       </c>
-      <c r="X34" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y34" s="1">
+      <c r="X34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z34" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z34" s="1"/>
-      <c r="AA34" s="1"/>
+      <c r="AA34" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
@@ -3855,13 +4021,14 @@
       <c r="AU34" s="1"/>
       <c r="AV34" s="1"/>
       <c r="AW34" s="1"/>
-    </row>
-    <row r="35" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX34" s="1"/>
+    </row>
+    <row r="35" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
@@ -3880,7 +4047,7 @@
         <v>150</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1">
@@ -3901,30 +4068,33 @@
       </c>
       <c r="Q35" s="5"/>
       <c r="R35" s="5"/>
-      <c r="S35" s="1">
+      <c r="S35" s="5"/>
+      <c r="T35" s="1">
         <f t="shared" si="4"/>
         <v>61.666666666666664</v>
       </c>
-      <c r="T35" s="1">
+      <c r="U35" s="1">
         <f t="shared" si="5"/>
         <v>61.666666666666664</v>
       </c>
-      <c r="U35" s="1">
+      <c r="V35" s="1">
         <v>1.8</v>
-      </c>
-      <c r="V35" s="1">
-        <v>0</v>
       </c>
       <c r="W35" s="1">
         <v>0</v>
       </c>
-      <c r="X35" s="1"/>
-      <c r="Y35" s="1">
+      <c r="X35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="1"/>
+      <c r="Z35" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z35" s="1"/>
-      <c r="AA35" s="1"/>
+      <c r="AA35" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
@@ -3947,13 +4117,14 @@
       <c r="AU35" s="1"/>
       <c r="AV35" s="1"/>
       <c r="AW35" s="1"/>
-    </row>
-    <row r="36" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX35" s="1"/>
+    </row>
+    <row r="36" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C36" s="1">
         <v>109</v>
@@ -3974,7 +4145,7 @@
         <v>150</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1">
@@ -3995,32 +4166,35 @@
       </c>
       <c r="Q36" s="5"/>
       <c r="R36" s="5"/>
-      <c r="S36" s="1">
+      <c r="S36" s="5"/>
+      <c r="T36" s="1">
         <f t="shared" si="4"/>
         <v>30.833333333333332</v>
       </c>
-      <c r="T36" s="1">
+      <c r="U36" s="1">
         <f t="shared" si="5"/>
         <v>30.833333333333332</v>
       </c>
-      <c r="U36" s="1">
+      <c r="V36" s="1">
         <v>10.199999999999999</v>
       </c>
-      <c r="V36" s="1">
+      <c r="W36" s="1">
         <v>3.6</v>
       </c>
-      <c r="W36" s="1">
+      <c r="X36" s="1">
         <v>4.8</v>
       </c>
-      <c r="X36" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y36" s="1">
+      <c r="Y36" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z36" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z36" s="1"/>
-      <c r="AA36" s="1"/>
+      <c r="AA36" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
@@ -4043,13 +4217,14 @@
       <c r="AU36" s="1"/>
       <c r="AV36" s="1"/>
       <c r="AW36" s="1"/>
-    </row>
-    <row r="37" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX36" s="1"/>
+    </row>
+    <row r="37" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C37" s="1">
         <v>29</v>
@@ -4070,7 +4245,7 @@
         <v>150</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1">
@@ -4090,34 +4265,40 @@
         <v>5.2</v>
       </c>
       <c r="Q37" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>37.400000000000006</v>
       </c>
-      <c r="R37" s="5"/>
-      <c r="S37" s="1">
+      <c r="R37" s="5">
+        <f>VLOOKUP(A37,заказ!A:B,2,0)</f>
+        <v>40</v>
+      </c>
+      <c r="S37" s="5"/>
+      <c r="T37" s="1">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="T37" s="1">
+      <c r="U37" s="1">
         <f t="shared" si="5"/>
         <v>9.8076923076923066</v>
       </c>
-      <c r="U37" s="1">
+      <c r="V37" s="1">
         <v>4.2</v>
-      </c>
-      <c r="V37" s="1">
-        <v>0</v>
       </c>
       <c r="W37" s="1">
         <v>0</v>
       </c>
-      <c r="X37" s="1"/>
-      <c r="Y37" s="1">
+      <c r="X37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="1"/>
+      <c r="Z37" s="1">
         <f t="shared" si="3"/>
         <v>6.7320000000000011</v>
       </c>
-      <c r="Z37" s="1"/>
-      <c r="AA37" s="1"/>
+      <c r="AA37" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
@@ -4140,13 +4321,14 @@
       <c r="AU37" s="1"/>
       <c r="AV37" s="1"/>
       <c r="AW37" s="1"/>
-    </row>
-    <row r="38" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX37" s="1"/>
+    </row>
+    <row r="38" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C38" s="1">
         <v>3</v>
@@ -4184,30 +4366,33 @@
       </c>
       <c r="Q38" s="5"/>
       <c r="R38" s="5"/>
-      <c r="S38" s="1">
+      <c r="S38" s="5"/>
+      <c r="T38" s="1">
         <f t="shared" si="4"/>
         <v>80</v>
       </c>
-      <c r="T38" s="1">
+      <c r="U38" s="1">
         <f t="shared" si="5"/>
         <v>80</v>
       </c>
-      <c r="U38" s="1">
+      <c r="V38" s="1">
         <v>0.8</v>
-      </c>
-      <c r="V38" s="1">
-        <v>0</v>
       </c>
       <c r="W38" s="1">
         <v>0</v>
       </c>
-      <c r="X38" s="1"/>
-      <c r="Y38" s="1">
+      <c r="X38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z38" s="1"/>
-      <c r="AA38" s="1"/>
+      <c r="AA38" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
@@ -4230,13 +4415,14 @@
       <c r="AU38" s="1"/>
       <c r="AV38" s="1"/>
       <c r="AW38" s="1"/>
-    </row>
-    <row r="39" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX38" s="1"/>
+    </row>
+    <row r="39" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C39" s="1">
         <v>28</v>
@@ -4273,34 +4459,40 @@
         <v>1.4</v>
       </c>
       <c r="Q39" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.7999999999999972</v>
       </c>
-      <c r="R39" s="5"/>
-      <c r="S39" s="1">
+      <c r="R39" s="5">
+        <f>VLOOKUP(A39,заказ!A:B,2,0)</f>
+        <v>16</v>
+      </c>
+      <c r="S39" s="5"/>
+      <c r="T39" s="1">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="T39" s="1">
+      <c r="U39" s="1">
         <f t="shared" si="5"/>
         <v>13.571428571428573</v>
       </c>
-      <c r="U39" s="1">
+      <c r="V39" s="1">
         <v>0.8</v>
-      </c>
-      <c r="V39" s="1">
-        <v>0</v>
       </c>
       <c r="W39" s="1">
         <v>0</v>
       </c>
-      <c r="X39" s="1"/>
-      <c r="Y39" s="1">
+      <c r="X39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1">
         <f t="shared" si="3"/>
         <v>0.67199999999999971</v>
       </c>
-      <c r="Z39" s="1"/>
-      <c r="AA39" s="1"/>
+      <c r="AA39" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
@@ -4323,13 +4515,14 @@
       <c r="AU39" s="1"/>
       <c r="AV39" s="1"/>
       <c r="AW39" s="1"/>
-    </row>
-    <row r="40" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX39" s="1"/>
+    </row>
+    <row r="40" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C40" s="1">
         <v>40</v>
@@ -4350,7 +4543,7 @@
         <v>270</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1">
@@ -4369,32 +4562,35 @@
       </c>
       <c r="Q40" s="5"/>
       <c r="R40" s="5"/>
-      <c r="S40" s="1">
+      <c r="S40" s="5"/>
+      <c r="T40" s="1">
         <f t="shared" si="4"/>
         <v>27.8</v>
       </c>
-      <c r="T40" s="1">
+      <c r="U40" s="1">
         <f t="shared" si="5"/>
         <v>27.8</v>
       </c>
-      <c r="U40" s="1">
+      <c r="V40" s="1">
         <v>1.6</v>
-      </c>
-      <c r="V40" s="1">
-        <v>0</v>
       </c>
       <c r="W40" s="1">
         <v>0</v>
       </c>
-      <c r="X40" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y40" s="1">
+      <c r="X40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z40" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z40" s="1"/>
-      <c r="AA40" s="1"/>
+      <c r="AA40" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
@@ -4417,13 +4613,14 @@
       <c r="AU40" s="1"/>
       <c r="AV40" s="1"/>
       <c r="AW40" s="1"/>
-    </row>
-    <row r="41" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX40" s="1"/>
+    </row>
+    <row r="41" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C41" s="1">
         <v>43.72</v>
@@ -4442,7 +4639,7 @@
         <v>180</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1">
@@ -4461,32 +4658,35 @@
       </c>
       <c r="Q41" s="5"/>
       <c r="R41" s="5"/>
-      <c r="S41" s="1" t="e">
+      <c r="S41" s="5"/>
+      <c r="T41" s="1" t="e">
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T41" s="1" t="e">
+      <c r="U41" s="1" t="e">
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="U41" s="1">
+      <c r="V41" s="1">
         <v>0.68559999999999999</v>
       </c>
-      <c r="V41" s="1">
+      <c r="W41" s="1">
         <v>0</v>
       </c>
-      <c r="W41" s="1">
+      <c r="X41" s="1">
         <v>1.946</v>
       </c>
-      <c r="X41" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="Y41" s="1">
+      <c r="Y41" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z41" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z41" s="1"/>
-      <c r="AA41" s="1"/>
+      <c r="AA41" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
@@ -4509,13 +4709,14 @@
       <c r="AU41" s="1"/>
       <c r="AV41" s="1"/>
       <c r="AW41" s="1"/>
-    </row>
-    <row r="42" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX41" s="1"/>
+    </row>
+    <row r="42" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C42" s="1">
         <v>15.694000000000001</v>
@@ -4536,7 +4737,7 @@
         <v>180</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1">
@@ -4555,32 +4756,35 @@
       </c>
       <c r="Q42" s="5"/>
       <c r="R42" s="5"/>
-      <c r="S42" s="1">
+      <c r="S42" s="5"/>
+      <c r="T42" s="1">
         <f t="shared" si="4"/>
         <v>27.313361864003802</v>
       </c>
-      <c r="T42" s="1">
+      <c r="U42" s="1">
         <f t="shared" si="5"/>
         <v>27.313361864003802</v>
       </c>
-      <c r="U42" s="1">
+      <c r="V42" s="1">
         <v>0.64880000000000004</v>
-      </c>
-      <c r="V42" s="1">
-        <v>0</v>
       </c>
       <c r="W42" s="1">
         <v>0</v>
       </c>
-      <c r="X42" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y42" s="1">
+      <c r="X42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z42" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z42" s="1"/>
-      <c r="AA42" s="1"/>
+      <c r="AA42" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
@@ -4603,13 +4807,14 @@
       <c r="AU42" s="1"/>
       <c r="AV42" s="1"/>
       <c r="AW42" s="1"/>
-    </row>
-    <row r="43" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX42" s="1"/>
+    </row>
+    <row r="43" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C43" s="1">
         <v>95.658000000000001</v>
@@ -4630,7 +4835,7 @@
         <v>180</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="1">
@@ -4649,32 +4854,35 @@
       </c>
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
-      <c r="S43" s="1">
+      <c r="S43" s="5"/>
+      <c r="T43" s="1">
         <f t="shared" si="4"/>
         <v>57.432675044883297</v>
       </c>
-      <c r="T43" s="1">
+      <c r="U43" s="1">
         <f t="shared" si="5"/>
         <v>57.432675044883297</v>
       </c>
-      <c r="U43" s="1">
+      <c r="V43" s="1">
         <v>1.2083999999999999</v>
-      </c>
-      <c r="V43" s="1">
-        <v>0</v>
       </c>
       <c r="W43" s="1">
         <v>0</v>
       </c>
-      <c r="X43" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y43" s="1">
+      <c r="X43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z43" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z43" s="1"/>
-      <c r="AA43" s="1"/>
+      <c r="AA43" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
@@ -4697,13 +4905,14 @@
       <c r="AU43" s="1"/>
       <c r="AV43" s="1"/>
       <c r="AW43" s="1"/>
-    </row>
-    <row r="44" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX43" s="1"/>
+    </row>
+    <row r="44" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C44" s="1">
         <v>16.318000000000001</v>
@@ -4724,7 +4933,7 @@
         <v>180</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J44" s="1"/>
       <c r="K44" s="1">
@@ -4743,32 +4952,35 @@
       </c>
       <c r="Q44" s="5"/>
       <c r="R44" s="5"/>
-      <c r="S44" s="1">
+      <c r="S44" s="5"/>
+      <c r="T44" s="1">
         <f t="shared" si="4"/>
         <v>114.25015954052328</v>
       </c>
-      <c r="T44" s="1">
+      <c r="U44" s="1">
         <f t="shared" si="5"/>
         <v>114.25015954052328</v>
       </c>
-      <c r="U44" s="1">
-        <v>0</v>
-      </c>
       <c r="V44" s="1">
         <v>0</v>
       </c>
       <c r="W44" s="1">
         <v>0</v>
       </c>
-      <c r="X44" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y44" s="1">
+      <c r="X44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z44" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z44" s="1"/>
-      <c r="AA44" s="1"/>
+      <c r="AA44" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
@@ -4791,13 +5003,14 @@
       <c r="AU44" s="1"/>
       <c r="AV44" s="1"/>
       <c r="AW44" s="1"/>
-    </row>
-    <row r="45" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX44" s="1"/>
+    </row>
+    <row r="45" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45" s="1">
         <v>261</v>
@@ -4834,34 +5047,40 @@
         <v>17.600000000000001</v>
       </c>
       <c r="Q45" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>59.200000000000045</v>
       </c>
-      <c r="R45" s="5"/>
-      <c r="S45" s="1">
+      <c r="R45" s="5">
+        <f>VLOOKUP(A45,заказ!A:B,2,0)</f>
+        <v>60</v>
+      </c>
+      <c r="S45" s="5"/>
+      <c r="T45" s="1">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="T45" s="1">
+      <c r="U45" s="1">
         <f t="shared" si="5"/>
         <v>13.636363636363635</v>
       </c>
-      <c r="U45" s="1">
+      <c r="V45" s="1">
         <v>12.6</v>
       </c>
-      <c r="V45" s="1">
+      <c r="W45" s="1">
         <v>20.399999999999999</v>
       </c>
-      <c r="W45" s="1">
+      <c r="X45" s="1">
         <v>7.2</v>
       </c>
-      <c r="X45" s="1"/>
-      <c r="Y45" s="1">
+      <c r="Y45" s="1"/>
+      <c r="Z45" s="1">
         <f t="shared" si="3"/>
         <v>5.9200000000000053</v>
       </c>
-      <c r="Z45" s="1"/>
-      <c r="AA45" s="1"/>
+      <c r="AA45" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
@@ -4884,13 +5103,14 @@
       <c r="AU45" s="1"/>
       <c r="AV45" s="1"/>
       <c r="AW45" s="1"/>
-    </row>
-    <row r="46" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX45" s="1"/>
+    </row>
+    <row r="46" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="1">
         <v>95</v>
@@ -4927,34 +5147,40 @@
         <v>19.8</v>
       </c>
       <c r="Q46" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>155.60000000000002</v>
       </c>
-      <c r="R46" s="5"/>
-      <c r="S46" s="1">
+      <c r="R46" s="5">
+        <f>VLOOKUP(A46,заказ!A:B,2,0)</f>
+        <v>156</v>
+      </c>
+      <c r="S46" s="5"/>
+      <c r="T46" s="1">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="T46" s="1">
+      <c r="U46" s="1">
         <f t="shared" si="5"/>
         <v>9.1414141414141419</v>
       </c>
-      <c r="U46" s="1">
+      <c r="V46" s="1">
         <v>14.8</v>
       </c>
-      <c r="V46" s="1">
+      <c r="W46" s="1">
         <v>19.399999999999999</v>
       </c>
-      <c r="W46" s="1">
+      <c r="X46" s="1">
         <v>11.4</v>
       </c>
-      <c r="X46" s="1"/>
-      <c r="Y46" s="1">
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1">
         <f t="shared" si="3"/>
         <v>15.560000000000002</v>
       </c>
-      <c r="Z46" s="1"/>
-      <c r="AA46" s="1"/>
+      <c r="AA46" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
@@ -4977,13 +5203,14 @@
       <c r="AU46" s="1"/>
       <c r="AV46" s="1"/>
       <c r="AW46" s="1"/>
-    </row>
-    <row r="47" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX46" s="1"/>
+    </row>
+    <row r="47" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C47" s="1">
         <v>11</v>
@@ -5021,32 +5248,35 @@
       </c>
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
-      <c r="S47" s="1">
+      <c r="S47" s="5"/>
+      <c r="T47" s="1">
         <f t="shared" si="4"/>
         <v>28.125</v>
       </c>
-      <c r="T47" s="1">
+      <c r="U47" s="1">
         <f t="shared" si="5"/>
         <v>28.125</v>
       </c>
-      <c r="U47" s="1">
+      <c r="V47" s="1">
         <v>1</v>
-      </c>
-      <c r="V47" s="1">
-        <v>0</v>
       </c>
       <c r="W47" s="1">
         <v>0</v>
       </c>
-      <c r="X47" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y47" s="1">
+      <c r="X47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z47" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z47" s="1"/>
-      <c r="AA47" s="1"/>
+      <c r="AA47" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
@@ -5069,13 +5299,14 @@
       <c r="AU47" s="1"/>
       <c r="AV47" s="1"/>
       <c r="AW47" s="1"/>
-    </row>
-    <row r="48" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX47" s="1"/>
+    </row>
+    <row r="48" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
@@ -5111,30 +5342,33 @@
       </c>
       <c r="Q48" s="5"/>
       <c r="R48" s="5"/>
-      <c r="S48" s="1">
+      <c r="S48" s="5"/>
+      <c r="T48" s="1">
         <f t="shared" si="4"/>
         <v>178.33333333333334</v>
       </c>
-      <c r="T48" s="1">
+      <c r="U48" s="1">
         <f t="shared" si="5"/>
         <v>178.33333333333334</v>
       </c>
-      <c r="U48" s="1">
-        <v>0</v>
-      </c>
       <c r="V48" s="1">
         <v>0</v>
       </c>
       <c r="W48" s="1">
         <v>0</v>
       </c>
-      <c r="X48" s="1"/>
-      <c r="Y48" s="1">
+      <c r="X48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z48" s="1"/>
-      <c r="AA48" s="1"/>
+      <c r="AA48" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
@@ -5157,13 +5391,14 @@
       <c r="AU48" s="1"/>
       <c r="AV48" s="1"/>
       <c r="AW48" s="1"/>
-    </row>
-    <row r="49" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX48" s="1"/>
+    </row>
+    <row r="49" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
@@ -5182,7 +5417,7 @@
         <v>120</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J49" s="1"/>
       <c r="K49" s="1">
@@ -5200,34 +5435,40 @@
         <v>3.1947999999999999</v>
       </c>
       <c r="Q49" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.1295999999999964</v>
       </c>
-      <c r="R49" s="5"/>
-      <c r="S49" s="1">
+      <c r="R49" s="5">
+        <f>VLOOKUP(A49,заказ!A:B,2,0)</f>
+        <v>15</v>
+      </c>
+      <c r="S49" s="5"/>
+      <c r="T49" s="1">
         <f t="shared" si="4"/>
         <v>17</v>
       </c>
-      <c r="T49" s="1">
+      <c r="U49" s="1">
         <f t="shared" si="5"/>
         <v>15.081382246149994</v>
       </c>
-      <c r="U49" s="1">
+      <c r="V49" s="1">
         <v>0.65359999999999996</v>
-      </c>
-      <c r="V49" s="1">
-        <v>0</v>
       </c>
       <c r="W49" s="1">
         <v>0</v>
       </c>
-      <c r="X49" s="1"/>
-      <c r="Y49" s="1">
+      <c r="X49" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="1"/>
+      <c r="Z49" s="1">
         <f t="shared" si="3"/>
         <v>6.1295999999999964</v>
       </c>
-      <c r="Z49" s="1"/>
-      <c r="AA49" s="1"/>
+      <c r="AA49" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
@@ -5250,13 +5491,14 @@
       <c r="AU49" s="1"/>
       <c r="AV49" s="1"/>
       <c r="AW49" s="1"/>
-    </row>
-    <row r="50" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX49" s="1"/>
+    </row>
+    <row r="50" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C50" s="1">
         <v>20</v>
@@ -5294,32 +5536,35 @@
       </c>
       <c r="Q50" s="5"/>
       <c r="R50" s="5"/>
-      <c r="S50" s="1">
+      <c r="S50" s="5"/>
+      <c r="T50" s="1">
         <f t="shared" si="4"/>
         <v>211.66666666666669</v>
       </c>
-      <c r="T50" s="1">
+      <c r="U50" s="1">
         <f t="shared" si="5"/>
         <v>211.66666666666669</v>
       </c>
-      <c r="U50" s="1">
-        <v>0</v>
-      </c>
       <c r="V50" s="1">
         <v>0</v>
       </c>
       <c r="W50" s="1">
         <v>0</v>
       </c>
-      <c r="X50" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y50" s="1">
+      <c r="X50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Z50" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z50" s="1"/>
-      <c r="AA50" s="1"/>
+      <c r="AA50" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
@@ -5342,13 +5587,14 @@
       <c r="AU50" s="1"/>
       <c r="AV50" s="1"/>
       <c r="AW50" s="1"/>
-    </row>
-    <row r="51" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX50" s="1"/>
+    </row>
+    <row r="51" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C51" s="1">
         <v>3.9039999999999999</v>
@@ -5369,7 +5615,7 @@
         <v>120</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1">
@@ -5388,30 +5634,33 @@
       </c>
       <c r="Q51" s="5"/>
       <c r="R51" s="5"/>
-      <c r="S51" s="1">
+      <c r="S51" s="5"/>
+      <c r="T51" s="1">
         <f t="shared" si="4"/>
         <v>35.534940411700973</v>
       </c>
-      <c r="T51" s="1">
+      <c r="U51" s="1">
         <f t="shared" si="5"/>
         <v>35.534940411700973</v>
       </c>
-      <c r="U51" s="1">
+      <c r="V51" s="1">
         <v>2.2936000000000001</v>
-      </c>
-      <c r="V51" s="1">
-        <v>0</v>
       </c>
       <c r="W51" s="1">
         <v>0</v>
       </c>
-      <c r="X51" s="1"/>
-      <c r="Y51" s="1">
+      <c r="X51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z51" s="1"/>
-      <c r="AA51" s="1"/>
+      <c r="AA51" s="1">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
@@ -5434,8 +5683,9 @@
       <c r="AU51" s="1"/>
       <c r="AV51" s="1"/>
       <c r="AW51" s="1"/>
-    </row>
-    <row r="52" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX51" s="1"/>
+    </row>
+    <row r="52" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -5485,8 +5735,9 @@
       <c r="AU52" s="1"/>
       <c r="AV52" s="1"/>
       <c r="AW52" s="1"/>
-    </row>
-    <row r="53" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX52" s="1"/>
+    </row>
+    <row r="53" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
@@ -5536,8 +5787,9 @@
       <c r="AU53" s="1"/>
       <c r="AV53" s="1"/>
       <c r="AW53" s="1"/>
-    </row>
-    <row r="54" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX53" s="1"/>
+    </row>
+    <row r="54" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
@@ -5587,8 +5839,9 @@
       <c r="AU54" s="1"/>
       <c r="AV54" s="1"/>
       <c r="AW54" s="1"/>
-    </row>
-    <row r="55" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX54" s="1"/>
+    </row>
+    <row r="55" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="C55" s="1"/>
@@ -5638,8 +5891,9 @@
       <c r="AU55" s="1"/>
       <c r="AV55" s="1"/>
       <c r="AW55" s="1"/>
-    </row>
-    <row r="56" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX55" s="1"/>
+    </row>
+    <row r="56" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>
@@ -5689,8 +5943,9 @@
       <c r="AU56" s="1"/>
       <c r="AV56" s="1"/>
       <c r="AW56" s="1"/>
-    </row>
-    <row r="57" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX56" s="1"/>
+    </row>
+    <row r="57" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="C57" s="1"/>
@@ -5740,8 +5995,9 @@
       <c r="AU57" s="1"/>
       <c r="AV57" s="1"/>
       <c r="AW57" s="1"/>
-    </row>
-    <row r="58" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX57" s="1"/>
+    </row>
+    <row r="58" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="C58" s="1"/>
@@ -5791,8 +6047,9 @@
       <c r="AU58" s="1"/>
       <c r="AV58" s="1"/>
       <c r="AW58" s="1"/>
-    </row>
-    <row r="59" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX58" s="1"/>
+    </row>
+    <row r="59" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="C59" s="1"/>
@@ -5842,8 +6099,9 @@
       <c r="AU59" s="1"/>
       <c r="AV59" s="1"/>
       <c r="AW59" s="1"/>
-    </row>
-    <row r="60" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX59" s="1"/>
+    </row>
+    <row r="60" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="C60" s="1"/>
@@ -5893,8 +6151,9 @@
       <c r="AU60" s="1"/>
       <c r="AV60" s="1"/>
       <c r="AW60" s="1"/>
-    </row>
-    <row r="61" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX60" s="1"/>
+    </row>
+    <row r="61" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="C61" s="1"/>
@@ -5944,8 +6203,9 @@
       <c r="AU61" s="1"/>
       <c r="AV61" s="1"/>
       <c r="AW61" s="1"/>
-    </row>
-    <row r="62" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX61" s="1"/>
+    </row>
+    <row r="62" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="C62" s="1"/>
@@ -5995,8 +6255,9 @@
       <c r="AU62" s="1"/>
       <c r="AV62" s="1"/>
       <c r="AW62" s="1"/>
-    </row>
-    <row r="63" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX62" s="1"/>
+    </row>
+    <row r="63" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
@@ -6046,8 +6307,9 @@
       <c r="AU63" s="1"/>
       <c r="AV63" s="1"/>
       <c r="AW63" s="1"/>
-    </row>
-    <row r="64" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX63" s="1"/>
+    </row>
+    <row r="64" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="C64" s="1"/>
@@ -6097,8 +6359,9 @@
       <c r="AU64" s="1"/>
       <c r="AV64" s="1"/>
       <c r="AW64" s="1"/>
-    </row>
-    <row r="65" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX64" s="1"/>
+    </row>
+    <row r="65" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="C65" s="1"/>
@@ -6148,8 +6411,9 @@
       <c r="AU65" s="1"/>
       <c r="AV65" s="1"/>
       <c r="AW65" s="1"/>
-    </row>
-    <row r="66" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX65" s="1"/>
+    </row>
+    <row r="66" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
@@ -6199,8 +6463,9 @@
       <c r="AU66" s="1"/>
       <c r="AV66" s="1"/>
       <c r="AW66" s="1"/>
-    </row>
-    <row r="67" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX66" s="1"/>
+    </row>
+    <row r="67" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="C67" s="1"/>
@@ -6250,8 +6515,9 @@
       <c r="AU67" s="1"/>
       <c r="AV67" s="1"/>
       <c r="AW67" s="1"/>
-    </row>
-    <row r="68" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX67" s="1"/>
+    </row>
+    <row r="68" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="C68" s="1"/>
@@ -6301,8 +6567,9 @@
       <c r="AU68" s="1"/>
       <c r="AV68" s="1"/>
       <c r="AW68" s="1"/>
-    </row>
-    <row r="69" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX68" s="1"/>
+    </row>
+    <row r="69" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="C69" s="1"/>
@@ -6352,8 +6619,9 @@
       <c r="AU69" s="1"/>
       <c r="AV69" s="1"/>
       <c r="AW69" s="1"/>
-    </row>
-    <row r="70" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX69" s="1"/>
+    </row>
+    <row r="70" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="C70" s="1"/>
@@ -6403,8 +6671,9 @@
       <c r="AU70" s="1"/>
       <c r="AV70" s="1"/>
       <c r="AW70" s="1"/>
-    </row>
-    <row r="71" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX70" s="1"/>
+    </row>
+    <row r="71" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="C71" s="1"/>
@@ -6454,8 +6723,9 @@
       <c r="AU71" s="1"/>
       <c r="AV71" s="1"/>
       <c r="AW71" s="1"/>
-    </row>
-    <row r="72" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX71" s="1"/>
+    </row>
+    <row r="72" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
@@ -6505,8 +6775,9 @@
       <c r="AU72" s="1"/>
       <c r="AV72" s="1"/>
       <c r="AW72" s="1"/>
-    </row>
-    <row r="73" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX72" s="1"/>
+    </row>
+    <row r="73" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="C73" s="1"/>
@@ -6556,8 +6827,9 @@
       <c r="AU73" s="1"/>
       <c r="AV73" s="1"/>
       <c r="AW73" s="1"/>
-    </row>
-    <row r="74" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX73" s="1"/>
+    </row>
+    <row r="74" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="C74" s="1"/>
@@ -6607,8 +6879,9 @@
       <c r="AU74" s="1"/>
       <c r="AV74" s="1"/>
       <c r="AW74" s="1"/>
-    </row>
-    <row r="75" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX74" s="1"/>
+    </row>
+    <row r="75" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="C75" s="1"/>
@@ -6658,8 +6931,9 @@
       <c r="AU75" s="1"/>
       <c r="AV75" s="1"/>
       <c r="AW75" s="1"/>
-    </row>
-    <row r="76" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX75" s="1"/>
+    </row>
+    <row r="76" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="C76" s="1"/>
@@ -6709,8 +6983,9 @@
       <c r="AU76" s="1"/>
       <c r="AV76" s="1"/>
       <c r="AW76" s="1"/>
-    </row>
-    <row r="77" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX76" s="1"/>
+    </row>
+    <row r="77" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="C77" s="1"/>
@@ -6760,8 +7035,9 @@
       <c r="AU77" s="1"/>
       <c r="AV77" s="1"/>
       <c r="AW77" s="1"/>
-    </row>
-    <row r="78" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX77" s="1"/>
+    </row>
+    <row r="78" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="C78" s="1"/>
@@ -6811,8 +7087,9 @@
       <c r="AU78" s="1"/>
       <c r="AV78" s="1"/>
       <c r="AW78" s="1"/>
-    </row>
-    <row r="79" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX78" s="1"/>
+    </row>
+    <row r="79" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="C79" s="1"/>
@@ -6862,8 +7139,9 @@
       <c r="AU79" s="1"/>
       <c r="AV79" s="1"/>
       <c r="AW79" s="1"/>
-    </row>
-    <row r="80" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX79" s="1"/>
+    </row>
+    <row r="80" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="C80" s="1"/>
@@ -6913,8 +7191,9 @@
       <c r="AU80" s="1"/>
       <c r="AV80" s="1"/>
       <c r="AW80" s="1"/>
-    </row>
-    <row r="81" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX80" s="1"/>
+    </row>
+    <row r="81" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="C81" s="1"/>
@@ -6964,8 +7243,9 @@
       <c r="AU81" s="1"/>
       <c r="AV81" s="1"/>
       <c r="AW81" s="1"/>
-    </row>
-    <row r="82" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX81" s="1"/>
+    </row>
+    <row r="82" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="C82" s="1"/>
@@ -7015,8 +7295,9 @@
       <c r="AU82" s="1"/>
       <c r="AV82" s="1"/>
       <c r="AW82" s="1"/>
-    </row>
-    <row r="83" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX82" s="1"/>
+    </row>
+    <row r="83" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="C83" s="1"/>
@@ -7066,8 +7347,9 @@
       <c r="AU83" s="1"/>
       <c r="AV83" s="1"/>
       <c r="AW83" s="1"/>
-    </row>
-    <row r="84" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX83" s="1"/>
+    </row>
+    <row r="84" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="C84" s="1"/>
@@ -7117,8 +7399,9 @@
       <c r="AU84" s="1"/>
       <c r="AV84" s="1"/>
       <c r="AW84" s="1"/>
-    </row>
-    <row r="85" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX84" s="1"/>
+    </row>
+    <row r="85" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="C85" s="1"/>
@@ -7168,8 +7451,9 @@
       <c r="AU85" s="1"/>
       <c r="AV85" s="1"/>
       <c r="AW85" s="1"/>
-    </row>
-    <row r="86" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX85" s="1"/>
+    </row>
+    <row r="86" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="C86" s="1"/>
@@ -7219,8 +7503,9 @@
       <c r="AU86" s="1"/>
       <c r="AV86" s="1"/>
       <c r="AW86" s="1"/>
-    </row>
-    <row r="87" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX86" s="1"/>
+    </row>
+    <row r="87" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="C87" s="1"/>
@@ -7270,8 +7555,9 @@
       <c r="AU87" s="1"/>
       <c r="AV87" s="1"/>
       <c r="AW87" s="1"/>
-    </row>
-    <row r="88" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX87" s="1"/>
+    </row>
+    <row r="88" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="C88" s="1"/>
@@ -7321,8 +7607,9 @@
       <c r="AU88" s="1"/>
       <c r="AV88" s="1"/>
       <c r="AW88" s="1"/>
-    </row>
-    <row r="89" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX88" s="1"/>
+    </row>
+    <row r="89" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="C89" s="1"/>
@@ -7372,8 +7659,9 @@
       <c r="AU89" s="1"/>
       <c r="AV89" s="1"/>
       <c r="AW89" s="1"/>
-    </row>
-    <row r="90" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX89" s="1"/>
+    </row>
+    <row r="90" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="C90" s="1"/>
@@ -7423,8 +7711,9 @@
       <c r="AU90" s="1"/>
       <c r="AV90" s="1"/>
       <c r="AW90" s="1"/>
-    </row>
-    <row r="91" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX90" s="1"/>
+    </row>
+    <row r="91" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
@@ -7474,8 +7763,9 @@
       <c r="AU91" s="1"/>
       <c r="AV91" s="1"/>
       <c r="AW91" s="1"/>
-    </row>
-    <row r="92" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX91" s="1"/>
+    </row>
+    <row r="92" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
@@ -7525,8 +7815,9 @@
       <c r="AU92" s="1"/>
       <c r="AV92" s="1"/>
       <c r="AW92" s="1"/>
-    </row>
-    <row r="93" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX92" s="1"/>
+    </row>
+    <row r="93" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
@@ -7576,8 +7867,9 @@
       <c r="AU93" s="1"/>
       <c r="AV93" s="1"/>
       <c r="AW93" s="1"/>
-    </row>
-    <row r="94" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX93" s="1"/>
+    </row>
+    <row r="94" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="C94" s="1"/>
@@ -7627,8 +7919,9 @@
       <c r="AU94" s="1"/>
       <c r="AV94" s="1"/>
       <c r="AW94" s="1"/>
-    </row>
-    <row r="95" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX94" s="1"/>
+    </row>
+    <row r="95" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="C95" s="1"/>
@@ -7678,8 +7971,9 @@
       <c r="AU95" s="1"/>
       <c r="AV95" s="1"/>
       <c r="AW95" s="1"/>
-    </row>
-    <row r="96" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX95" s="1"/>
+    </row>
+    <row r="96" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="C96" s="1"/>
@@ -7729,8 +8023,9 @@
       <c r="AU96" s="1"/>
       <c r="AV96" s="1"/>
       <c r="AW96" s="1"/>
-    </row>
-    <row r="97" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX96" s="1"/>
+    </row>
+    <row r="97" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="C97" s="1"/>
@@ -7780,8 +8075,9 @@
       <c r="AU97" s="1"/>
       <c r="AV97" s="1"/>
       <c r="AW97" s="1"/>
-    </row>
-    <row r="98" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX97" s="1"/>
+    </row>
+    <row r="98" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="C98" s="1"/>
@@ -7831,8 +8127,9 @@
       <c r="AU98" s="1"/>
       <c r="AV98" s="1"/>
       <c r="AW98" s="1"/>
-    </row>
-    <row r="99" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX98" s="1"/>
+    </row>
+    <row r="99" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="C99" s="1"/>
@@ -7882,8 +8179,9 @@
       <c r="AU99" s="1"/>
       <c r="AV99" s="1"/>
       <c r="AW99" s="1"/>
-    </row>
-    <row r="100" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX99" s="1"/>
+    </row>
+    <row r="100" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="C100" s="1"/>
@@ -7933,8 +8231,9 @@
       <c r="AU100" s="1"/>
       <c r="AV100" s="1"/>
       <c r="AW100" s="1"/>
-    </row>
-    <row r="101" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX100" s="1"/>
+    </row>
+    <row r="101" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="C101" s="1"/>
@@ -7984,8 +8283,9 @@
       <c r="AU101" s="1"/>
       <c r="AV101" s="1"/>
       <c r="AW101" s="1"/>
-    </row>
-    <row r="102" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX101" s="1"/>
+    </row>
+    <row r="102" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="C102" s="1"/>
@@ -8035,8 +8335,9 @@
       <c r="AU102" s="1"/>
       <c r="AV102" s="1"/>
       <c r="AW102" s="1"/>
-    </row>
-    <row r="103" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX102" s="1"/>
+    </row>
+    <row r="103" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="C103" s="1"/>
@@ -8086,8 +8387,9 @@
       <c r="AU103" s="1"/>
       <c r="AV103" s="1"/>
       <c r="AW103" s="1"/>
-    </row>
-    <row r="104" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX103" s="1"/>
+    </row>
+    <row r="104" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="C104" s="1"/>
@@ -8137,8 +8439,9 @@
       <c r="AU104" s="1"/>
       <c r="AV104" s="1"/>
       <c r="AW104" s="1"/>
-    </row>
-    <row r="105" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX104" s="1"/>
+    </row>
+    <row r="105" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="C105" s="1"/>
@@ -8188,8 +8491,9 @@
       <c r="AU105" s="1"/>
       <c r="AV105" s="1"/>
       <c r="AW105" s="1"/>
-    </row>
-    <row r="106" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX105" s="1"/>
+    </row>
+    <row r="106" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="C106" s="1"/>
@@ -8239,8 +8543,9 @@
       <c r="AU106" s="1"/>
       <c r="AV106" s="1"/>
       <c r="AW106" s="1"/>
-    </row>
-    <row r="107" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX106" s="1"/>
+    </row>
+    <row r="107" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="C107" s="1"/>
@@ -8290,8 +8595,9 @@
       <c r="AU107" s="1"/>
       <c r="AV107" s="1"/>
       <c r="AW107" s="1"/>
-    </row>
-    <row r="108" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX107" s="1"/>
+    </row>
+    <row r="108" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
@@ -8341,8 +8647,9 @@
       <c r="AU108" s="1"/>
       <c r="AV108" s="1"/>
       <c r="AW108" s="1"/>
-    </row>
-    <row r="109" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX108" s="1"/>
+    </row>
+    <row r="109" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="C109" s="1"/>
@@ -8392,8 +8699,9 @@
       <c r="AU109" s="1"/>
       <c r="AV109" s="1"/>
       <c r="AW109" s="1"/>
-    </row>
-    <row r="110" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX109" s="1"/>
+    </row>
+    <row r="110" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="C110" s="1"/>
@@ -8443,8 +8751,9 @@
       <c r="AU110" s="1"/>
       <c r="AV110" s="1"/>
       <c r="AW110" s="1"/>
-    </row>
-    <row r="111" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX110" s="1"/>
+    </row>
+    <row r="111" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="C111" s="1"/>
@@ -8494,8 +8803,9 @@
       <c r="AU111" s="1"/>
       <c r="AV111" s="1"/>
       <c r="AW111" s="1"/>
-    </row>
-    <row r="112" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX111" s="1"/>
+    </row>
+    <row r="112" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="C112" s="1"/>
@@ -8545,8 +8855,9 @@
       <c r="AU112" s="1"/>
       <c r="AV112" s="1"/>
       <c r="AW112" s="1"/>
-    </row>
-    <row r="113" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX112" s="1"/>
+    </row>
+    <row r="113" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="C113" s="1"/>
@@ -8596,8 +8907,9 @@
       <c r="AU113" s="1"/>
       <c r="AV113" s="1"/>
       <c r="AW113" s="1"/>
-    </row>
-    <row r="114" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX113" s="1"/>
+    </row>
+    <row r="114" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="C114" s="1"/>
@@ -8647,8 +8959,9 @@
       <c r="AU114" s="1"/>
       <c r="AV114" s="1"/>
       <c r="AW114" s="1"/>
-    </row>
-    <row r="115" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX114" s="1"/>
+    </row>
+    <row r="115" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="C115" s="1"/>
@@ -8698,8 +9011,9 @@
       <c r="AU115" s="1"/>
       <c r="AV115" s="1"/>
       <c r="AW115" s="1"/>
-    </row>
-    <row r="116" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX115" s="1"/>
+    </row>
+    <row r="116" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
@@ -8749,8 +9063,9 @@
       <c r="AU116" s="1"/>
       <c r="AV116" s="1"/>
       <c r="AW116" s="1"/>
-    </row>
-    <row r="117" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX116" s="1"/>
+    </row>
+    <row r="117" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="C117" s="1"/>
@@ -8800,8 +9115,9 @@
       <c r="AU117" s="1"/>
       <c r="AV117" s="1"/>
       <c r="AW117" s="1"/>
-    </row>
-    <row r="118" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX117" s="1"/>
+    </row>
+    <row r="118" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="C118" s="1"/>
@@ -8851,8 +9167,9 @@
       <c r="AU118" s="1"/>
       <c r="AV118" s="1"/>
       <c r="AW118" s="1"/>
-    </row>
-    <row r="119" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX118" s="1"/>
+    </row>
+    <row r="119" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="C119" s="1"/>
@@ -8902,8 +9219,9 @@
       <c r="AU119" s="1"/>
       <c r="AV119" s="1"/>
       <c r="AW119" s="1"/>
-    </row>
-    <row r="120" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX119" s="1"/>
+    </row>
+    <row r="120" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="C120" s="1"/>
@@ -8953,8 +9271,9 @@
       <c r="AU120" s="1"/>
       <c r="AV120" s="1"/>
       <c r="AW120" s="1"/>
-    </row>
-    <row r="121" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX120" s="1"/>
+    </row>
+    <row r="121" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
@@ -9004,8 +9323,9 @@
       <c r="AU121" s="1"/>
       <c r="AV121" s="1"/>
       <c r="AW121" s="1"/>
-    </row>
-    <row r="122" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX121" s="1"/>
+    </row>
+    <row r="122" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="C122" s="1"/>
@@ -9055,8 +9375,9 @@
       <c r="AU122" s="1"/>
       <c r="AV122" s="1"/>
       <c r="AW122" s="1"/>
-    </row>
-    <row r="123" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX122" s="1"/>
+    </row>
+    <row r="123" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="C123" s="1"/>
@@ -9106,8 +9427,9 @@
       <c r="AU123" s="1"/>
       <c r="AV123" s="1"/>
       <c r="AW123" s="1"/>
-    </row>
-    <row r="124" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX123" s="1"/>
+    </row>
+    <row r="124" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
@@ -9157,8 +9479,9 @@
       <c r="AU124" s="1"/>
       <c r="AV124" s="1"/>
       <c r="AW124" s="1"/>
-    </row>
-    <row r="125" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX124" s="1"/>
+    </row>
+    <row r="125" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
@@ -9208,8 +9531,9 @@
       <c r="AU125" s="1"/>
       <c r="AV125" s="1"/>
       <c r="AW125" s="1"/>
-    </row>
-    <row r="126" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX125" s="1"/>
+    </row>
+    <row r="126" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="C126" s="1"/>
@@ -9259,8 +9583,9 @@
       <c r="AU126" s="1"/>
       <c r="AV126" s="1"/>
       <c r="AW126" s="1"/>
-    </row>
-    <row r="127" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX126" s="1"/>
+    </row>
+    <row r="127" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="C127" s="1"/>
@@ -9310,8 +9635,9 @@
       <c r="AU127" s="1"/>
       <c r="AV127" s="1"/>
       <c r="AW127" s="1"/>
-    </row>
-    <row r="128" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX127" s="1"/>
+    </row>
+    <row r="128" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="C128" s="1"/>
@@ -9361,8 +9687,9 @@
       <c r="AU128" s="1"/>
       <c r="AV128" s="1"/>
       <c r="AW128" s="1"/>
-    </row>
-    <row r="129" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX128" s="1"/>
+    </row>
+    <row r="129" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="C129" s="1"/>
@@ -9412,8 +9739,9 @@
       <c r="AU129" s="1"/>
       <c r="AV129" s="1"/>
       <c r="AW129" s="1"/>
-    </row>
-    <row r="130" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX129" s="1"/>
+    </row>
+    <row r="130" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
@@ -9463,8 +9791,9 @@
       <c r="AU130" s="1"/>
       <c r="AV130" s="1"/>
       <c r="AW130" s="1"/>
-    </row>
-    <row r="131" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX130" s="1"/>
+    </row>
+    <row r="131" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="C131" s="1"/>
@@ -9514,8 +9843,9 @@
       <c r="AU131" s="1"/>
       <c r="AV131" s="1"/>
       <c r="AW131" s="1"/>
-    </row>
-    <row r="132" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX131" s="1"/>
+    </row>
+    <row r="132" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="C132" s="1"/>
@@ -9565,8 +9895,9 @@
       <c r="AU132" s="1"/>
       <c r="AV132" s="1"/>
       <c r="AW132" s="1"/>
-    </row>
-    <row r="133" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX132" s="1"/>
+    </row>
+    <row r="133" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="C133" s="1"/>
@@ -9616,8 +9947,9 @@
       <c r="AU133" s="1"/>
       <c r="AV133" s="1"/>
       <c r="AW133" s="1"/>
-    </row>
-    <row r="134" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX133" s="1"/>
+    </row>
+    <row r="134" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="C134" s="1"/>
@@ -9667,8 +9999,9 @@
       <c r="AU134" s="1"/>
       <c r="AV134" s="1"/>
       <c r="AW134" s="1"/>
-    </row>
-    <row r="135" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX134" s="1"/>
+    </row>
+    <row r="135" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="C135" s="1"/>
@@ -9718,8 +10051,9 @@
       <c r="AU135" s="1"/>
       <c r="AV135" s="1"/>
       <c r="AW135" s="1"/>
-    </row>
-    <row r="136" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX135" s="1"/>
+    </row>
+    <row r="136" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="C136" s="1"/>
@@ -9769,8 +10103,9 @@
       <c r="AU136" s="1"/>
       <c r="AV136" s="1"/>
       <c r="AW136" s="1"/>
-    </row>
-    <row r="137" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX136" s="1"/>
+    </row>
+    <row r="137" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="C137" s="1"/>
@@ -9820,8 +10155,9 @@
       <c r="AU137" s="1"/>
       <c r="AV137" s="1"/>
       <c r="AW137" s="1"/>
-    </row>
-    <row r="138" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX137" s="1"/>
+    </row>
+    <row r="138" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="C138" s="1"/>
@@ -9871,8 +10207,9 @@
       <c r="AU138" s="1"/>
       <c r="AV138" s="1"/>
       <c r="AW138" s="1"/>
-    </row>
-    <row r="139" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX138" s="1"/>
+    </row>
+    <row r="139" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="C139" s="1"/>
@@ -9922,8 +10259,9 @@
       <c r="AU139" s="1"/>
       <c r="AV139" s="1"/>
       <c r="AW139" s="1"/>
-    </row>
-    <row r="140" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX139" s="1"/>
+    </row>
+    <row r="140" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="C140" s="1"/>
@@ -9973,8 +10311,9 @@
       <c r="AU140" s="1"/>
       <c r="AV140" s="1"/>
       <c r="AW140" s="1"/>
-    </row>
-    <row r="141" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX140" s="1"/>
+    </row>
+    <row r="141" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="C141" s="1"/>
@@ -10024,8 +10363,9 @@
       <c r="AU141" s="1"/>
       <c r="AV141" s="1"/>
       <c r="AW141" s="1"/>
-    </row>
-    <row r="142" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX141" s="1"/>
+    </row>
+    <row r="142" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="C142" s="1"/>
@@ -10075,8 +10415,9 @@
       <c r="AU142" s="1"/>
       <c r="AV142" s="1"/>
       <c r="AW142" s="1"/>
-    </row>
-    <row r="143" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX142" s="1"/>
+    </row>
+    <row r="143" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="C143" s="1"/>
@@ -10126,8 +10467,9 @@
       <c r="AU143" s="1"/>
       <c r="AV143" s="1"/>
       <c r="AW143" s="1"/>
-    </row>
-    <row r="144" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX143" s="1"/>
+    </row>
+    <row r="144" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="C144" s="1"/>
@@ -10177,8 +10519,9 @@
       <c r="AU144" s="1"/>
       <c r="AV144" s="1"/>
       <c r="AW144" s="1"/>
-    </row>
-    <row r="145" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX144" s="1"/>
+    </row>
+    <row r="145" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="C145" s="1"/>
@@ -10228,8 +10571,9 @@
       <c r="AU145" s="1"/>
       <c r="AV145" s="1"/>
       <c r="AW145" s="1"/>
-    </row>
-    <row r="146" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX145" s="1"/>
+    </row>
+    <row r="146" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="C146" s="1"/>
@@ -10279,8 +10623,9 @@
       <c r="AU146" s="1"/>
       <c r="AV146" s="1"/>
       <c r="AW146" s="1"/>
-    </row>
-    <row r="147" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX146" s="1"/>
+    </row>
+    <row r="147" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="C147" s="1"/>
@@ -10330,8 +10675,9 @@
       <c r="AU147" s="1"/>
       <c r="AV147" s="1"/>
       <c r="AW147" s="1"/>
-    </row>
-    <row r="148" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX147" s="1"/>
+    </row>
+    <row r="148" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="C148" s="1"/>
@@ -10381,8 +10727,9 @@
       <c r="AU148" s="1"/>
       <c r="AV148" s="1"/>
       <c r="AW148" s="1"/>
-    </row>
-    <row r="149" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX148" s="1"/>
+    </row>
+    <row r="149" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="C149" s="1"/>
@@ -10432,8 +10779,9 @@
       <c r="AU149" s="1"/>
       <c r="AV149" s="1"/>
       <c r="AW149" s="1"/>
-    </row>
-    <row r="150" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX149" s="1"/>
+    </row>
+    <row r="150" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="C150" s="1"/>
@@ -10483,8 +10831,9 @@
       <c r="AU150" s="1"/>
       <c r="AV150" s="1"/>
       <c r="AW150" s="1"/>
-    </row>
-    <row r="151" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX150" s="1"/>
+    </row>
+    <row r="151" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="C151" s="1"/>
@@ -10534,8 +10883,9 @@
       <c r="AU151" s="1"/>
       <c r="AV151" s="1"/>
       <c r="AW151" s="1"/>
-    </row>
-    <row r="152" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX151" s="1"/>
+    </row>
+    <row r="152" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="C152" s="1"/>
@@ -10585,8 +10935,9 @@
       <c r="AU152" s="1"/>
       <c r="AV152" s="1"/>
       <c r="AW152" s="1"/>
-    </row>
-    <row r="153" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX152" s="1"/>
+    </row>
+    <row r="153" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="C153" s="1"/>
@@ -10636,8 +10987,9 @@
       <c r="AU153" s="1"/>
       <c r="AV153" s="1"/>
       <c r="AW153" s="1"/>
-    </row>
-    <row r="154" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX153" s="1"/>
+    </row>
+    <row r="154" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="C154" s="1"/>
@@ -10687,8 +11039,9 @@
       <c r="AU154" s="1"/>
       <c r="AV154" s="1"/>
       <c r="AW154" s="1"/>
-    </row>
-    <row r="155" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX154" s="1"/>
+    </row>
+    <row r="155" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="C155" s="1"/>
@@ -10738,8 +11091,9 @@
       <c r="AU155" s="1"/>
       <c r="AV155" s="1"/>
       <c r="AW155" s="1"/>
-    </row>
-    <row r="156" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX155" s="1"/>
+    </row>
+    <row r="156" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="C156" s="1"/>
@@ -10789,8 +11143,9 @@
       <c r="AU156" s="1"/>
       <c r="AV156" s="1"/>
       <c r="AW156" s="1"/>
-    </row>
-    <row r="157" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX156" s="1"/>
+    </row>
+    <row r="157" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="C157" s="1"/>
@@ -10840,8 +11195,9 @@
       <c r="AU157" s="1"/>
       <c r="AV157" s="1"/>
       <c r="AW157" s="1"/>
-    </row>
-    <row r="158" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX157" s="1"/>
+    </row>
+    <row r="158" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="C158" s="1"/>
@@ -10891,8 +11247,9 @@
       <c r="AU158" s="1"/>
       <c r="AV158" s="1"/>
       <c r="AW158" s="1"/>
-    </row>
-    <row r="159" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX158" s="1"/>
+    </row>
+    <row r="159" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="C159" s="1"/>
@@ -10942,8 +11299,9 @@
       <c r="AU159" s="1"/>
       <c r="AV159" s="1"/>
       <c r="AW159" s="1"/>
-    </row>
-    <row r="160" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX159" s="1"/>
+    </row>
+    <row r="160" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="C160" s="1"/>
@@ -10993,8 +11351,9 @@
       <c r="AU160" s="1"/>
       <c r="AV160" s="1"/>
       <c r="AW160" s="1"/>
-    </row>
-    <row r="161" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX160" s="1"/>
+    </row>
+    <row r="161" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="C161" s="1"/>
@@ -11044,8 +11403,9 @@
       <c r="AU161" s="1"/>
       <c r="AV161" s="1"/>
       <c r="AW161" s="1"/>
-    </row>
-    <row r="162" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX161" s="1"/>
+    </row>
+    <row r="162" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="C162" s="1"/>
@@ -11095,8 +11455,9 @@
       <c r="AU162" s="1"/>
       <c r="AV162" s="1"/>
       <c r="AW162" s="1"/>
-    </row>
-    <row r="163" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX162" s="1"/>
+    </row>
+    <row r="163" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="C163" s="1"/>
@@ -11146,8 +11507,9 @@
       <c r="AU163" s="1"/>
       <c r="AV163" s="1"/>
       <c r="AW163" s="1"/>
-    </row>
-    <row r="164" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX163" s="1"/>
+    </row>
+    <row r="164" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="C164" s="1"/>
@@ -11197,8 +11559,9 @@
       <c r="AU164" s="1"/>
       <c r="AV164" s="1"/>
       <c r="AW164" s="1"/>
-    </row>
-    <row r="165" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX164" s="1"/>
+    </row>
+    <row r="165" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="C165" s="1"/>
@@ -11248,8 +11611,9 @@
       <c r="AU165" s="1"/>
       <c r="AV165" s="1"/>
       <c r="AW165" s="1"/>
-    </row>
-    <row r="166" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX165" s="1"/>
+    </row>
+    <row r="166" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="C166" s="1"/>
@@ -11299,8 +11663,9 @@
       <c r="AU166" s="1"/>
       <c r="AV166" s="1"/>
       <c r="AW166" s="1"/>
-    </row>
-    <row r="167" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX166" s="1"/>
+    </row>
+    <row r="167" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="C167" s="1"/>
@@ -11350,8 +11715,9 @@
       <c r="AU167" s="1"/>
       <c r="AV167" s="1"/>
       <c r="AW167" s="1"/>
-    </row>
-    <row r="168" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX167" s="1"/>
+    </row>
+    <row r="168" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="C168" s="1"/>
@@ -11401,8 +11767,9 @@
       <c r="AU168" s="1"/>
       <c r="AV168" s="1"/>
       <c r="AW168" s="1"/>
-    </row>
-    <row r="169" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX168" s="1"/>
+    </row>
+    <row r="169" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="C169" s="1"/>
@@ -11452,8 +11819,9 @@
       <c r="AU169" s="1"/>
       <c r="AV169" s="1"/>
       <c r="AW169" s="1"/>
-    </row>
-    <row r="170" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX169" s="1"/>
+    </row>
+    <row r="170" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="C170" s="1"/>
@@ -11503,8 +11871,9 @@
       <c r="AU170" s="1"/>
       <c r="AV170" s="1"/>
       <c r="AW170" s="1"/>
-    </row>
-    <row r="171" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX170" s="1"/>
+    </row>
+    <row r="171" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="C171" s="1"/>
@@ -11554,8 +11923,9 @@
       <c r="AU171" s="1"/>
       <c r="AV171" s="1"/>
       <c r="AW171" s="1"/>
-    </row>
-    <row r="172" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX171" s="1"/>
+    </row>
+    <row r="172" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="C172" s="1"/>
@@ -11605,8 +11975,9 @@
       <c r="AU172" s="1"/>
       <c r="AV172" s="1"/>
       <c r="AW172" s="1"/>
-    </row>
-    <row r="173" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX172" s="1"/>
+    </row>
+    <row r="173" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="C173" s="1"/>
@@ -11656,8 +12027,9 @@
       <c r="AU173" s="1"/>
       <c r="AV173" s="1"/>
       <c r="AW173" s="1"/>
-    </row>
-    <row r="174" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX173" s="1"/>
+    </row>
+    <row r="174" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="C174" s="1"/>
@@ -11707,8 +12079,9 @@
       <c r="AU174" s="1"/>
       <c r="AV174" s="1"/>
       <c r="AW174" s="1"/>
-    </row>
-    <row r="175" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX174" s="1"/>
+    </row>
+    <row r="175" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="C175" s="1"/>
@@ -11758,8 +12131,9 @@
       <c r="AU175" s="1"/>
       <c r="AV175" s="1"/>
       <c r="AW175" s="1"/>
-    </row>
-    <row r="176" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX175" s="1"/>
+    </row>
+    <row r="176" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="C176" s="1"/>
@@ -11809,8 +12183,9 @@
       <c r="AU176" s="1"/>
       <c r="AV176" s="1"/>
       <c r="AW176" s="1"/>
-    </row>
-    <row r="177" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX176" s="1"/>
+    </row>
+    <row r="177" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="C177" s="1"/>
@@ -11860,8 +12235,9 @@
       <c r="AU177" s="1"/>
       <c r="AV177" s="1"/>
       <c r="AW177" s="1"/>
-    </row>
-    <row r="178" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX177" s="1"/>
+    </row>
+    <row r="178" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="C178" s="1"/>
@@ -11911,8 +12287,9 @@
       <c r="AU178" s="1"/>
       <c r="AV178" s="1"/>
       <c r="AW178" s="1"/>
-    </row>
-    <row r="179" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX178" s="1"/>
+    </row>
+    <row r="179" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="C179" s="1"/>
@@ -11962,8 +12339,9 @@
       <c r="AU179" s="1"/>
       <c r="AV179" s="1"/>
       <c r="AW179" s="1"/>
-    </row>
-    <row r="180" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX179" s="1"/>
+    </row>
+    <row r="180" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="C180" s="1"/>
@@ -12013,8 +12391,9 @@
       <c r="AU180" s="1"/>
       <c r="AV180" s="1"/>
       <c r="AW180" s="1"/>
-    </row>
-    <row r="181" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX180" s="1"/>
+    </row>
+    <row r="181" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="C181" s="1"/>
@@ -12064,8 +12443,9 @@
       <c r="AU181" s="1"/>
       <c r="AV181" s="1"/>
       <c r="AW181" s="1"/>
-    </row>
-    <row r="182" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX181" s="1"/>
+    </row>
+    <row r="182" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="C182" s="1"/>
@@ -12115,8 +12495,9 @@
       <c r="AU182" s="1"/>
       <c r="AV182" s="1"/>
       <c r="AW182" s="1"/>
-    </row>
-    <row r="183" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX182" s="1"/>
+    </row>
+    <row r="183" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="C183" s="1"/>
@@ -12166,8 +12547,9 @@
       <c r="AU183" s="1"/>
       <c r="AV183" s="1"/>
       <c r="AW183" s="1"/>
-    </row>
-    <row r="184" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX183" s="1"/>
+    </row>
+    <row r="184" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="C184" s="1"/>
@@ -12217,8 +12599,9 @@
       <c r="AU184" s="1"/>
       <c r="AV184" s="1"/>
       <c r="AW184" s="1"/>
-    </row>
-    <row r="185" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX184" s="1"/>
+    </row>
+    <row r="185" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="C185" s="1"/>
@@ -12268,8 +12651,9 @@
       <c r="AU185" s="1"/>
       <c r="AV185" s="1"/>
       <c r="AW185" s="1"/>
-    </row>
-    <row r="186" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX185" s="1"/>
+    </row>
+    <row r="186" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="C186" s="1"/>
@@ -12319,8 +12703,9 @@
       <c r="AU186" s="1"/>
       <c r="AV186" s="1"/>
       <c r="AW186" s="1"/>
-    </row>
-    <row r="187" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX186" s="1"/>
+    </row>
+    <row r="187" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="C187" s="1"/>
@@ -12370,8 +12755,9 @@
       <c r="AU187" s="1"/>
       <c r="AV187" s="1"/>
       <c r="AW187" s="1"/>
-    </row>
-    <row r="188" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX187" s="1"/>
+    </row>
+    <row r="188" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="C188" s="1"/>
@@ -12421,8 +12807,9 @@
       <c r="AU188" s="1"/>
       <c r="AV188" s="1"/>
       <c r="AW188" s="1"/>
-    </row>
-    <row r="189" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX188" s="1"/>
+    </row>
+    <row r="189" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="C189" s="1"/>
@@ -12472,8 +12859,9 @@
       <c r="AU189" s="1"/>
       <c r="AV189" s="1"/>
       <c r="AW189" s="1"/>
-    </row>
-    <row r="190" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX189" s="1"/>
+    </row>
+    <row r="190" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="C190" s="1"/>
@@ -12523,8 +12911,9 @@
       <c r="AU190" s="1"/>
       <c r="AV190" s="1"/>
       <c r="AW190" s="1"/>
-    </row>
-    <row r="191" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX190" s="1"/>
+    </row>
+    <row r="191" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="C191" s="1"/>
@@ -12574,8 +12963,9 @@
       <c r="AU191" s="1"/>
       <c r="AV191" s="1"/>
       <c r="AW191" s="1"/>
-    </row>
-    <row r="192" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX191" s="1"/>
+    </row>
+    <row r="192" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="C192" s="1"/>
@@ -12625,8 +13015,9 @@
       <c r="AU192" s="1"/>
       <c r="AV192" s="1"/>
       <c r="AW192" s="1"/>
-    </row>
-    <row r="193" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX192" s="1"/>
+    </row>
+    <row r="193" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="C193" s="1"/>
@@ -12676,8 +13067,9 @@
       <c r="AU193" s="1"/>
       <c r="AV193" s="1"/>
       <c r="AW193" s="1"/>
-    </row>
-    <row r="194" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX193" s="1"/>
+    </row>
+    <row r="194" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="C194" s="1"/>
@@ -12727,8 +13119,9 @@
       <c r="AU194" s="1"/>
       <c r="AV194" s="1"/>
       <c r="AW194" s="1"/>
-    </row>
-    <row r="195" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX194" s="1"/>
+    </row>
+    <row r="195" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="C195" s="1"/>
@@ -12778,8 +13171,9 @@
       <c r="AU195" s="1"/>
       <c r="AV195" s="1"/>
       <c r="AW195" s="1"/>
-    </row>
-    <row r="196" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX195" s="1"/>
+    </row>
+    <row r="196" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="C196" s="1"/>
@@ -12829,8 +13223,9 @@
       <c r="AU196" s="1"/>
       <c r="AV196" s="1"/>
       <c r="AW196" s="1"/>
-    </row>
-    <row r="197" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX196" s="1"/>
+    </row>
+    <row r="197" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="C197" s="1"/>
@@ -12880,8 +13275,9 @@
       <c r="AU197" s="1"/>
       <c r="AV197" s="1"/>
       <c r="AW197" s="1"/>
-    </row>
-    <row r="198" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX197" s="1"/>
+    </row>
+    <row r="198" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="C198" s="1"/>
@@ -12931,8 +13327,9 @@
       <c r="AU198" s="1"/>
       <c r="AV198" s="1"/>
       <c r="AW198" s="1"/>
-    </row>
-    <row r="199" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX198" s="1"/>
+    </row>
+    <row r="199" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="C199" s="1"/>
@@ -12982,8 +13379,9 @@
       <c r="AU199" s="1"/>
       <c r="AV199" s="1"/>
       <c r="AW199" s="1"/>
-    </row>
-    <row r="200" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX199" s="1"/>
+    </row>
+    <row r="200" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="C200" s="1"/>
@@ -13033,8 +13431,9 @@
       <c r="AU200" s="1"/>
       <c r="AV200" s="1"/>
       <c r="AW200" s="1"/>
-    </row>
-    <row r="201" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX200" s="1"/>
+    </row>
+    <row r="201" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="C201" s="1"/>
@@ -13084,8 +13483,9 @@
       <c r="AU201" s="1"/>
       <c r="AV201" s="1"/>
       <c r="AW201" s="1"/>
-    </row>
-    <row r="202" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX201" s="1"/>
+    </row>
+    <row r="202" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="C202" s="1"/>
@@ -13135,8 +13535,9 @@
       <c r="AU202" s="1"/>
       <c r="AV202" s="1"/>
       <c r="AW202" s="1"/>
-    </row>
-    <row r="203" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX202" s="1"/>
+    </row>
+    <row r="203" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="C203" s="1"/>
@@ -13186,8 +13587,9 @@
       <c r="AU203" s="1"/>
       <c r="AV203" s="1"/>
       <c r="AW203" s="1"/>
-    </row>
-    <row r="204" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX203" s="1"/>
+    </row>
+    <row r="204" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="C204" s="1"/>
@@ -13237,8 +13639,9 @@
       <c r="AU204" s="1"/>
       <c r="AV204" s="1"/>
       <c r="AW204" s="1"/>
-    </row>
-    <row r="205" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX204" s="1"/>
+    </row>
+    <row r="205" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="C205" s="1"/>
@@ -13288,8 +13691,9 @@
       <c r="AU205" s="1"/>
       <c r="AV205" s="1"/>
       <c r="AW205" s="1"/>
-    </row>
-    <row r="206" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX205" s="1"/>
+    </row>
+    <row r="206" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="C206" s="1"/>
@@ -13339,8 +13743,9 @@
       <c r="AU206" s="1"/>
       <c r="AV206" s="1"/>
       <c r="AW206" s="1"/>
-    </row>
-    <row r="207" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX206" s="1"/>
+    </row>
+    <row r="207" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="C207" s="1"/>
@@ -13390,8 +13795,9 @@
       <c r="AU207" s="1"/>
       <c r="AV207" s="1"/>
       <c r="AW207" s="1"/>
-    </row>
-    <row r="208" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX207" s="1"/>
+    </row>
+    <row r="208" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="C208" s="1"/>
@@ -13441,8 +13847,9 @@
       <c r="AU208" s="1"/>
       <c r="AV208" s="1"/>
       <c r="AW208" s="1"/>
-    </row>
-    <row r="209" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX208" s="1"/>
+    </row>
+    <row r="209" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="C209" s="1"/>
@@ -13492,8 +13899,9 @@
       <c r="AU209" s="1"/>
       <c r="AV209" s="1"/>
       <c r="AW209" s="1"/>
-    </row>
-    <row r="210" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX209" s="1"/>
+    </row>
+    <row r="210" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="C210" s="1"/>
@@ -13543,8 +13951,9 @@
       <c r="AU210" s="1"/>
       <c r="AV210" s="1"/>
       <c r="AW210" s="1"/>
-    </row>
-    <row r="211" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX210" s="1"/>
+    </row>
+    <row r="211" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="C211" s="1"/>
@@ -13594,8 +14003,9 @@
       <c r="AU211" s="1"/>
       <c r="AV211" s="1"/>
       <c r="AW211" s="1"/>
-    </row>
-    <row r="212" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX211" s="1"/>
+    </row>
+    <row r="212" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="C212" s="1"/>
@@ -13645,8 +14055,9 @@
       <c r="AU212" s="1"/>
       <c r="AV212" s="1"/>
       <c r="AW212" s="1"/>
-    </row>
-    <row r="213" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX212" s="1"/>
+    </row>
+    <row r="213" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="C213" s="1"/>
@@ -13696,8 +14107,9 @@
       <c r="AU213" s="1"/>
       <c r="AV213" s="1"/>
       <c r="AW213" s="1"/>
-    </row>
-    <row r="214" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX213" s="1"/>
+    </row>
+    <row r="214" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="C214" s="1"/>
@@ -13747,8 +14159,9 @@
       <c r="AU214" s="1"/>
       <c r="AV214" s="1"/>
       <c r="AW214" s="1"/>
-    </row>
-    <row r="215" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX214" s="1"/>
+    </row>
+    <row r="215" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="C215" s="1"/>
@@ -13798,8 +14211,9 @@
       <c r="AU215" s="1"/>
       <c r="AV215" s="1"/>
       <c r="AW215" s="1"/>
-    </row>
-    <row r="216" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX215" s="1"/>
+    </row>
+    <row r="216" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="C216" s="1"/>
@@ -13849,8 +14263,9 @@
       <c r="AU216" s="1"/>
       <c r="AV216" s="1"/>
       <c r="AW216" s="1"/>
-    </row>
-    <row r="217" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX216" s="1"/>
+    </row>
+    <row r="217" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="C217" s="1"/>
@@ -13900,8 +14315,9 @@
       <c r="AU217" s="1"/>
       <c r="AV217" s="1"/>
       <c r="AW217" s="1"/>
-    </row>
-    <row r="218" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX217" s="1"/>
+    </row>
+    <row r="218" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="C218" s="1"/>
@@ -13951,8 +14367,9 @@
       <c r="AU218" s="1"/>
       <c r="AV218" s="1"/>
       <c r="AW218" s="1"/>
-    </row>
-    <row r="219" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX218" s="1"/>
+    </row>
+    <row r="219" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="C219" s="1"/>
@@ -14002,8 +14419,9 @@
       <c r="AU219" s="1"/>
       <c r="AV219" s="1"/>
       <c r="AW219" s="1"/>
-    </row>
-    <row r="220" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX219" s="1"/>
+    </row>
+    <row r="220" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="C220" s="1"/>
@@ -14053,8 +14471,9 @@
       <c r="AU220" s="1"/>
       <c r="AV220" s="1"/>
       <c r="AW220" s="1"/>
-    </row>
-    <row r="221" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX220" s="1"/>
+    </row>
+    <row r="221" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="C221" s="1"/>
@@ -14104,8 +14523,9 @@
       <c r="AU221" s="1"/>
       <c r="AV221" s="1"/>
       <c r="AW221" s="1"/>
-    </row>
-    <row r="222" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX221" s="1"/>
+    </row>
+    <row r="222" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="C222" s="1"/>
@@ -14155,8 +14575,9 @@
       <c r="AU222" s="1"/>
       <c r="AV222" s="1"/>
       <c r="AW222" s="1"/>
-    </row>
-    <row r="223" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX222" s="1"/>
+    </row>
+    <row r="223" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="C223" s="1"/>
@@ -14206,8 +14627,9 @@
       <c r="AU223" s="1"/>
       <c r="AV223" s="1"/>
       <c r="AW223" s="1"/>
-    </row>
-    <row r="224" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX223" s="1"/>
+    </row>
+    <row r="224" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="C224" s="1"/>
@@ -14257,8 +14679,9 @@
       <c r="AU224" s="1"/>
       <c r="AV224" s="1"/>
       <c r="AW224" s="1"/>
-    </row>
-    <row r="225" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX224" s="1"/>
+    </row>
+    <row r="225" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="C225" s="1"/>
@@ -14308,8 +14731,9 @@
       <c r="AU225" s="1"/>
       <c r="AV225" s="1"/>
       <c r="AW225" s="1"/>
-    </row>
-    <row r="226" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX225" s="1"/>
+    </row>
+    <row r="226" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="C226" s="1"/>
@@ -14359,8 +14783,9 @@
       <c r="AU226" s="1"/>
       <c r="AV226" s="1"/>
       <c r="AW226" s="1"/>
-    </row>
-    <row r="227" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX226" s="1"/>
+    </row>
+    <row r="227" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="C227" s="1"/>
@@ -14410,8 +14835,9 @@
       <c r="AU227" s="1"/>
       <c r="AV227" s="1"/>
       <c r="AW227" s="1"/>
-    </row>
-    <row r="228" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX227" s="1"/>
+    </row>
+    <row r="228" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="C228" s="1"/>
@@ -14461,8 +14887,9 @@
       <c r="AU228" s="1"/>
       <c r="AV228" s="1"/>
       <c r="AW228" s="1"/>
-    </row>
-    <row r="229" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX228" s="1"/>
+    </row>
+    <row r="229" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="C229" s="1"/>
@@ -14512,8 +14939,9 @@
       <c r="AU229" s="1"/>
       <c r="AV229" s="1"/>
       <c r="AW229" s="1"/>
-    </row>
-    <row r="230" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX229" s="1"/>
+    </row>
+    <row r="230" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="C230" s="1"/>
@@ -14563,8 +14991,9 @@
       <c r="AU230" s="1"/>
       <c r="AV230" s="1"/>
       <c r="AW230" s="1"/>
-    </row>
-    <row r="231" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX230" s="1"/>
+    </row>
+    <row r="231" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="C231" s="1"/>
@@ -14614,8 +15043,9 @@
       <c r="AU231" s="1"/>
       <c r="AV231" s="1"/>
       <c r="AW231" s="1"/>
-    </row>
-    <row r="232" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX231" s="1"/>
+    </row>
+    <row r="232" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="C232" s="1"/>
@@ -14665,8 +15095,9 @@
       <c r="AU232" s="1"/>
       <c r="AV232" s="1"/>
       <c r="AW232" s="1"/>
-    </row>
-    <row r="233" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX232" s="1"/>
+    </row>
+    <row r="233" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="C233" s="1"/>
@@ -14716,8 +15147,9 @@
       <c r="AU233" s="1"/>
       <c r="AV233" s="1"/>
       <c r="AW233" s="1"/>
-    </row>
-    <row r="234" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX233" s="1"/>
+    </row>
+    <row r="234" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="C234" s="1"/>
@@ -14767,8 +15199,9 @@
       <c r="AU234" s="1"/>
       <c r="AV234" s="1"/>
       <c r="AW234" s="1"/>
-    </row>
-    <row r="235" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX234" s="1"/>
+    </row>
+    <row r="235" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="C235" s="1"/>
@@ -14818,8 +15251,9 @@
       <c r="AU235" s="1"/>
       <c r="AV235" s="1"/>
       <c r="AW235" s="1"/>
-    </row>
-    <row r="236" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX235" s="1"/>
+    </row>
+    <row r="236" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="C236" s="1"/>
@@ -14869,8 +15303,9 @@
       <c r="AU236" s="1"/>
       <c r="AV236" s="1"/>
       <c r="AW236" s="1"/>
-    </row>
-    <row r="237" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX236" s="1"/>
+    </row>
+    <row r="237" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="C237" s="1"/>
@@ -14920,8 +15355,9 @@
       <c r="AU237" s="1"/>
       <c r="AV237" s="1"/>
       <c r="AW237" s="1"/>
-    </row>
-    <row r="238" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX237" s="1"/>
+    </row>
+    <row r="238" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="C238" s="1"/>
@@ -14971,8 +15407,9 @@
       <c r="AU238" s="1"/>
       <c r="AV238" s="1"/>
       <c r="AW238" s="1"/>
-    </row>
-    <row r="239" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX238" s="1"/>
+    </row>
+    <row r="239" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="C239" s="1"/>
@@ -15022,8 +15459,9 @@
       <c r="AU239" s="1"/>
       <c r="AV239" s="1"/>
       <c r="AW239" s="1"/>
-    </row>
-    <row r="240" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX239" s="1"/>
+    </row>
+    <row r="240" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="C240" s="1"/>
@@ -15073,8 +15511,9 @@
       <c r="AU240" s="1"/>
       <c r="AV240" s="1"/>
       <c r="AW240" s="1"/>
-    </row>
-    <row r="241" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX240" s="1"/>
+    </row>
+    <row r="241" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="C241" s="1"/>
@@ -15124,8 +15563,9 @@
       <c r="AU241" s="1"/>
       <c r="AV241" s="1"/>
       <c r="AW241" s="1"/>
-    </row>
-    <row r="242" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX241" s="1"/>
+    </row>
+    <row r="242" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="C242" s="1"/>
@@ -15175,8 +15615,9 @@
       <c r="AU242" s="1"/>
       <c r="AV242" s="1"/>
       <c r="AW242" s="1"/>
-    </row>
-    <row r="243" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX242" s="1"/>
+    </row>
+    <row r="243" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="C243" s="1"/>
@@ -15226,8 +15667,9 @@
       <c r="AU243" s="1"/>
       <c r="AV243" s="1"/>
       <c r="AW243" s="1"/>
-    </row>
-    <row r="244" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX243" s="1"/>
+    </row>
+    <row r="244" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="C244" s="1"/>
@@ -15277,8 +15719,9 @@
       <c r="AU244" s="1"/>
       <c r="AV244" s="1"/>
       <c r="AW244" s="1"/>
-    </row>
-    <row r="245" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX244" s="1"/>
+    </row>
+    <row r="245" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="C245" s="1"/>
@@ -15328,8 +15771,9 @@
       <c r="AU245" s="1"/>
       <c r="AV245" s="1"/>
       <c r="AW245" s="1"/>
-    </row>
-    <row r="246" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX245" s="1"/>
+    </row>
+    <row r="246" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="C246" s="1"/>
@@ -15379,8 +15823,9 @@
       <c r="AU246" s="1"/>
       <c r="AV246" s="1"/>
       <c r="AW246" s="1"/>
-    </row>
-    <row r="247" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX246" s="1"/>
+    </row>
+    <row r="247" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="C247" s="1"/>
@@ -15430,8 +15875,9 @@
       <c r="AU247" s="1"/>
       <c r="AV247" s="1"/>
       <c r="AW247" s="1"/>
-    </row>
-    <row r="248" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX247" s="1"/>
+    </row>
+    <row r="248" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="C248" s="1"/>
@@ -15481,8 +15927,9 @@
       <c r="AU248" s="1"/>
       <c r="AV248" s="1"/>
       <c r="AW248" s="1"/>
-    </row>
-    <row r="249" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX248" s="1"/>
+    </row>
+    <row r="249" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="C249" s="1"/>
@@ -15532,8 +15979,9 @@
       <c r="AU249" s="1"/>
       <c r="AV249" s="1"/>
       <c r="AW249" s="1"/>
-    </row>
-    <row r="250" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX249" s="1"/>
+    </row>
+    <row r="250" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="C250" s="1"/>
@@ -15583,8 +16031,9 @@
       <c r="AU250" s="1"/>
       <c r="AV250" s="1"/>
       <c r="AW250" s="1"/>
-    </row>
-    <row r="251" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX250" s="1"/>
+    </row>
+    <row r="251" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="C251" s="1"/>
@@ -15634,8 +16083,9 @@
       <c r="AU251" s="1"/>
       <c r="AV251" s="1"/>
       <c r="AW251" s="1"/>
-    </row>
-    <row r="252" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX251" s="1"/>
+    </row>
+    <row r="252" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="C252" s="1"/>
@@ -15685,8 +16135,9 @@
       <c r="AU252" s="1"/>
       <c r="AV252" s="1"/>
       <c r="AW252" s="1"/>
-    </row>
-    <row r="253" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX252" s="1"/>
+    </row>
+    <row r="253" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="C253" s="1"/>
@@ -15736,8 +16187,9 @@
       <c r="AU253" s="1"/>
       <c r="AV253" s="1"/>
       <c r="AW253" s="1"/>
-    </row>
-    <row r="254" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX253" s="1"/>
+    </row>
+    <row r="254" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="C254" s="1"/>
@@ -15787,8 +16239,9 @@
       <c r="AU254" s="1"/>
       <c r="AV254" s="1"/>
       <c r="AW254" s="1"/>
-    </row>
-    <row r="255" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX254" s="1"/>
+    </row>
+    <row r="255" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="C255" s="1"/>
@@ -15838,8 +16291,9 @@
       <c r="AU255" s="1"/>
       <c r="AV255" s="1"/>
       <c r="AW255" s="1"/>
-    </row>
-    <row r="256" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX255" s="1"/>
+    </row>
+    <row r="256" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="C256" s="1"/>
@@ -15889,8 +16343,9 @@
       <c r="AU256" s="1"/>
       <c r="AV256" s="1"/>
       <c r="AW256" s="1"/>
-    </row>
-    <row r="257" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX256" s="1"/>
+    </row>
+    <row r="257" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="C257" s="1"/>
@@ -15940,8 +16395,9 @@
       <c r="AU257" s="1"/>
       <c r="AV257" s="1"/>
       <c r="AW257" s="1"/>
-    </row>
-    <row r="258" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX257" s="1"/>
+    </row>
+    <row r="258" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="C258" s="1"/>
@@ -15991,8 +16447,9 @@
       <c r="AU258" s="1"/>
       <c r="AV258" s="1"/>
       <c r="AW258" s="1"/>
-    </row>
-    <row r="259" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX258" s="1"/>
+    </row>
+    <row r="259" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="C259" s="1"/>
@@ -16042,8 +16499,9 @@
       <c r="AU259" s="1"/>
       <c r="AV259" s="1"/>
       <c r="AW259" s="1"/>
-    </row>
-    <row r="260" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX259" s="1"/>
+    </row>
+    <row r="260" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="C260" s="1"/>
@@ -16093,8 +16551,9 @@
       <c r="AU260" s="1"/>
       <c r="AV260" s="1"/>
       <c r="AW260" s="1"/>
-    </row>
-    <row r="261" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX260" s="1"/>
+    </row>
+    <row r="261" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="C261" s="1"/>
@@ -16144,8 +16603,9 @@
       <c r="AU261" s="1"/>
       <c r="AV261" s="1"/>
       <c r="AW261" s="1"/>
-    </row>
-    <row r="262" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX261" s="1"/>
+    </row>
+    <row r="262" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="C262" s="1"/>
@@ -16195,8 +16655,9 @@
       <c r="AU262" s="1"/>
       <c r="AV262" s="1"/>
       <c r="AW262" s="1"/>
-    </row>
-    <row r="263" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX262" s="1"/>
+    </row>
+    <row r="263" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="C263" s="1"/>
@@ -16246,8 +16707,9 @@
       <c r="AU263" s="1"/>
       <c r="AV263" s="1"/>
       <c r="AW263" s="1"/>
-    </row>
-    <row r="264" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX263" s="1"/>
+    </row>
+    <row r="264" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="C264" s="1"/>
@@ -16297,8 +16759,9 @@
       <c r="AU264" s="1"/>
       <c r="AV264" s="1"/>
       <c r="AW264" s="1"/>
-    </row>
-    <row r="265" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX264" s="1"/>
+    </row>
+    <row r="265" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="C265" s="1"/>
@@ -16348,8 +16811,9 @@
       <c r="AU265" s="1"/>
       <c r="AV265" s="1"/>
       <c r="AW265" s="1"/>
-    </row>
-    <row r="266" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX265" s="1"/>
+    </row>
+    <row r="266" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="C266" s="1"/>
@@ -16399,8 +16863,9 @@
       <c r="AU266" s="1"/>
       <c r="AV266" s="1"/>
       <c r="AW266" s="1"/>
-    </row>
-    <row r="267" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX266" s="1"/>
+    </row>
+    <row r="267" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="C267" s="1"/>
@@ -16450,8 +16915,9 @@
       <c r="AU267" s="1"/>
       <c r="AV267" s="1"/>
       <c r="AW267" s="1"/>
-    </row>
-    <row r="268" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX267" s="1"/>
+    </row>
+    <row r="268" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="C268" s="1"/>
@@ -16501,8 +16967,9 @@
       <c r="AU268" s="1"/>
       <c r="AV268" s="1"/>
       <c r="AW268" s="1"/>
-    </row>
-    <row r="269" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX268" s="1"/>
+    </row>
+    <row r="269" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="C269" s="1"/>
@@ -16552,8 +17019,9 @@
       <c r="AU269" s="1"/>
       <c r="AV269" s="1"/>
       <c r="AW269" s="1"/>
-    </row>
-    <row r="270" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX269" s="1"/>
+    </row>
+    <row r="270" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="C270" s="1"/>
@@ -16603,8 +17071,9 @@
       <c r="AU270" s="1"/>
       <c r="AV270" s="1"/>
       <c r="AW270" s="1"/>
-    </row>
-    <row r="271" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX270" s="1"/>
+    </row>
+    <row r="271" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="C271" s="1"/>
@@ -16654,8 +17123,9 @@
       <c r="AU271" s="1"/>
       <c r="AV271" s="1"/>
       <c r="AW271" s="1"/>
-    </row>
-    <row r="272" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX271" s="1"/>
+    </row>
+    <row r="272" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="C272" s="1"/>
@@ -16705,8 +17175,9 @@
       <c r="AU272" s="1"/>
       <c r="AV272" s="1"/>
       <c r="AW272" s="1"/>
-    </row>
-    <row r="273" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX272" s="1"/>
+    </row>
+    <row r="273" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="C273" s="1"/>
@@ -16756,8 +17227,9 @@
       <c r="AU273" s="1"/>
       <c r="AV273" s="1"/>
       <c r="AW273" s="1"/>
-    </row>
-    <row r="274" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX273" s="1"/>
+    </row>
+    <row r="274" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="C274" s="1"/>
@@ -16807,8 +17279,9 @@
       <c r="AU274" s="1"/>
       <c r="AV274" s="1"/>
       <c r="AW274" s="1"/>
-    </row>
-    <row r="275" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX274" s="1"/>
+    </row>
+    <row r="275" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="C275" s="1"/>
@@ -16858,8 +17331,9 @@
       <c r="AU275" s="1"/>
       <c r="AV275" s="1"/>
       <c r="AW275" s="1"/>
-    </row>
-    <row r="276" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX275" s="1"/>
+    </row>
+    <row r="276" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="C276" s="1"/>
@@ -16909,8 +17383,9 @@
       <c r="AU276" s="1"/>
       <c r="AV276" s="1"/>
       <c r="AW276" s="1"/>
-    </row>
-    <row r="277" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX276" s="1"/>
+    </row>
+    <row r="277" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="C277" s="1"/>
@@ -16960,8 +17435,9 @@
       <c r="AU277" s="1"/>
       <c r="AV277" s="1"/>
       <c r="AW277" s="1"/>
-    </row>
-    <row r="278" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX277" s="1"/>
+    </row>
+    <row r="278" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="C278" s="1"/>
@@ -17011,8 +17487,9 @@
       <c r="AU278" s="1"/>
       <c r="AV278" s="1"/>
       <c r="AW278" s="1"/>
-    </row>
-    <row r="279" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX278" s="1"/>
+    </row>
+    <row r="279" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="C279" s="1"/>
@@ -17062,8 +17539,9 @@
       <c r="AU279" s="1"/>
       <c r="AV279" s="1"/>
       <c r="AW279" s="1"/>
-    </row>
-    <row r="280" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX279" s="1"/>
+    </row>
+    <row r="280" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="C280" s="1"/>
@@ -17113,8 +17591,9 @@
       <c r="AU280" s="1"/>
       <c r="AV280" s="1"/>
       <c r="AW280" s="1"/>
-    </row>
-    <row r="281" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX280" s="1"/>
+    </row>
+    <row r="281" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="C281" s="1"/>
@@ -17164,8 +17643,9 @@
       <c r="AU281" s="1"/>
       <c r="AV281" s="1"/>
       <c r="AW281" s="1"/>
-    </row>
-    <row r="282" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX281" s="1"/>
+    </row>
+    <row r="282" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="C282" s="1"/>
@@ -17215,8 +17695,9 @@
       <c r="AU282" s="1"/>
       <c r="AV282" s="1"/>
       <c r="AW282" s="1"/>
-    </row>
-    <row r="283" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX282" s="1"/>
+    </row>
+    <row r="283" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="C283" s="1"/>
@@ -17266,8 +17747,9 @@
       <c r="AU283" s="1"/>
       <c r="AV283" s="1"/>
       <c r="AW283" s="1"/>
-    </row>
-    <row r="284" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX283" s="1"/>
+    </row>
+    <row r="284" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="C284" s="1"/>
@@ -17317,8 +17799,9 @@
       <c r="AU284" s="1"/>
       <c r="AV284" s="1"/>
       <c r="AW284" s="1"/>
-    </row>
-    <row r="285" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX284" s="1"/>
+    </row>
+    <row r="285" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="C285" s="1"/>
@@ -17368,8 +17851,9 @@
       <c r="AU285" s="1"/>
       <c r="AV285" s="1"/>
       <c r="AW285" s="1"/>
-    </row>
-    <row r="286" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX285" s="1"/>
+    </row>
+    <row r="286" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="C286" s="1"/>
@@ -17419,8 +17903,9 @@
       <c r="AU286" s="1"/>
       <c r="AV286" s="1"/>
       <c r="AW286" s="1"/>
-    </row>
-    <row r="287" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX286" s="1"/>
+    </row>
+    <row r="287" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="C287" s="1"/>
@@ -17470,8 +17955,9 @@
       <c r="AU287" s="1"/>
       <c r="AV287" s="1"/>
       <c r="AW287" s="1"/>
-    </row>
-    <row r="288" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX287" s="1"/>
+    </row>
+    <row r="288" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="C288" s="1"/>
@@ -17521,8 +18007,9 @@
       <c r="AU288" s="1"/>
       <c r="AV288" s="1"/>
       <c r="AW288" s="1"/>
-    </row>
-    <row r="289" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX288" s="1"/>
+    </row>
+    <row r="289" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="C289" s="1"/>
@@ -17572,8 +18059,9 @@
       <c r="AU289" s="1"/>
       <c r="AV289" s="1"/>
       <c r="AW289" s="1"/>
-    </row>
-    <row r="290" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX289" s="1"/>
+    </row>
+    <row r="290" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="C290" s="1"/>
@@ -17623,8 +18111,9 @@
       <c r="AU290" s="1"/>
       <c r="AV290" s="1"/>
       <c r="AW290" s="1"/>
-    </row>
-    <row r="291" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX290" s="1"/>
+    </row>
+    <row r="291" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="C291" s="1"/>
@@ -17674,8 +18163,9 @@
       <c r="AU291" s="1"/>
       <c r="AV291" s="1"/>
       <c r="AW291" s="1"/>
-    </row>
-    <row r="292" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX291" s="1"/>
+    </row>
+    <row r="292" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="C292" s="1"/>
@@ -17725,8 +18215,9 @@
       <c r="AU292" s="1"/>
       <c r="AV292" s="1"/>
       <c r="AW292" s="1"/>
-    </row>
-    <row r="293" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX292" s="1"/>
+    </row>
+    <row r="293" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="C293" s="1"/>
@@ -17776,8 +18267,9 @@
       <c r="AU293" s="1"/>
       <c r="AV293" s="1"/>
       <c r="AW293" s="1"/>
-    </row>
-    <row r="294" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX293" s="1"/>
+    </row>
+    <row r="294" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="C294" s="1"/>
@@ -17827,8 +18319,9 @@
       <c r="AU294" s="1"/>
       <c r="AV294" s="1"/>
       <c r="AW294" s="1"/>
-    </row>
-    <row r="295" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX294" s="1"/>
+    </row>
+    <row r="295" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="C295" s="1"/>
@@ -17878,8 +18371,9 @@
       <c r="AU295" s="1"/>
       <c r="AV295" s="1"/>
       <c r="AW295" s="1"/>
-    </row>
-    <row r="296" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX295" s="1"/>
+    </row>
+    <row r="296" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="C296" s="1"/>
@@ -17929,8 +18423,9 @@
       <c r="AU296" s="1"/>
       <c r="AV296" s="1"/>
       <c r="AW296" s="1"/>
-    </row>
-    <row r="297" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX296" s="1"/>
+    </row>
+    <row r="297" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="C297" s="1"/>
@@ -17980,8 +18475,9 @@
       <c r="AU297" s="1"/>
       <c r="AV297" s="1"/>
       <c r="AW297" s="1"/>
-    </row>
-    <row r="298" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX297" s="1"/>
+    </row>
+    <row r="298" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="C298" s="1"/>
@@ -18031,8 +18527,9 @@
       <c r="AU298" s="1"/>
       <c r="AV298" s="1"/>
       <c r="AW298" s="1"/>
-    </row>
-    <row r="299" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX298" s="1"/>
+    </row>
+    <row r="299" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="C299" s="1"/>
@@ -18082,8 +18579,9 @@
       <c r="AU299" s="1"/>
       <c r="AV299" s="1"/>
       <c r="AW299" s="1"/>
-    </row>
-    <row r="300" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX299" s="1"/>
+    </row>
+    <row r="300" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="C300" s="1"/>
@@ -18133,8 +18631,9 @@
       <c r="AU300" s="1"/>
       <c r="AV300" s="1"/>
       <c r="AW300" s="1"/>
-    </row>
-    <row r="301" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX300" s="1"/>
+    </row>
+    <row r="301" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="C301" s="1"/>
@@ -18184,8 +18683,9 @@
       <c r="AU301" s="1"/>
       <c r="AV301" s="1"/>
       <c r="AW301" s="1"/>
-    </row>
-    <row r="302" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX301" s="1"/>
+    </row>
+    <row r="302" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="C302" s="1"/>
@@ -18235,8 +18735,9 @@
       <c r="AU302" s="1"/>
       <c r="AV302" s="1"/>
       <c r="AW302" s="1"/>
-    </row>
-    <row r="303" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX302" s="1"/>
+    </row>
+    <row r="303" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="C303" s="1"/>
@@ -18286,8 +18787,9 @@
       <c r="AU303" s="1"/>
       <c r="AV303" s="1"/>
       <c r="AW303" s="1"/>
-    </row>
-    <row r="304" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX303" s="1"/>
+    </row>
+    <row r="304" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="C304" s="1"/>
@@ -18337,8 +18839,9 @@
       <c r="AU304" s="1"/>
       <c r="AV304" s="1"/>
       <c r="AW304" s="1"/>
-    </row>
-    <row r="305" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX304" s="1"/>
+    </row>
+    <row r="305" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="C305" s="1"/>
@@ -18388,8 +18891,9 @@
       <c r="AU305" s="1"/>
       <c r="AV305" s="1"/>
       <c r="AW305" s="1"/>
-    </row>
-    <row r="306" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX305" s="1"/>
+    </row>
+    <row r="306" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="C306" s="1"/>
@@ -18439,8 +18943,9 @@
       <c r="AU306" s="1"/>
       <c r="AV306" s="1"/>
       <c r="AW306" s="1"/>
-    </row>
-    <row r="307" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX306" s="1"/>
+    </row>
+    <row r="307" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="C307" s="1"/>
@@ -18490,8 +18995,9 @@
       <c r="AU307" s="1"/>
       <c r="AV307" s="1"/>
       <c r="AW307" s="1"/>
-    </row>
-    <row r="308" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX307" s="1"/>
+    </row>
+    <row r="308" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="C308" s="1"/>
@@ -18541,8 +19047,9 @@
       <c r="AU308" s="1"/>
       <c r="AV308" s="1"/>
       <c r="AW308" s="1"/>
-    </row>
-    <row r="309" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX308" s="1"/>
+    </row>
+    <row r="309" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="C309" s="1"/>
@@ -18592,8 +19099,9 @@
       <c r="AU309" s="1"/>
       <c r="AV309" s="1"/>
       <c r="AW309" s="1"/>
-    </row>
-    <row r="310" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX309" s="1"/>
+    </row>
+    <row r="310" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="C310" s="1"/>
@@ -18643,8 +19151,9 @@
       <c r="AU310" s="1"/>
       <c r="AV310" s="1"/>
       <c r="AW310" s="1"/>
-    </row>
-    <row r="311" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX310" s="1"/>
+    </row>
+    <row r="311" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="C311" s="1"/>
@@ -18694,8 +19203,9 @@
       <c r="AU311" s="1"/>
       <c r="AV311" s="1"/>
       <c r="AW311" s="1"/>
-    </row>
-    <row r="312" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX311" s="1"/>
+    </row>
+    <row r="312" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="C312" s="1"/>
@@ -18745,8 +19255,9 @@
       <c r="AU312" s="1"/>
       <c r="AV312" s="1"/>
       <c r="AW312" s="1"/>
-    </row>
-    <row r="313" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX312" s="1"/>
+    </row>
+    <row r="313" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="C313" s="1"/>
@@ -18796,8 +19307,9 @@
       <c r="AU313" s="1"/>
       <c r="AV313" s="1"/>
       <c r="AW313" s="1"/>
-    </row>
-    <row r="314" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX313" s="1"/>
+    </row>
+    <row r="314" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="C314" s="1"/>
@@ -18847,8 +19359,9 @@
       <c r="AU314" s="1"/>
       <c r="AV314" s="1"/>
       <c r="AW314" s="1"/>
-    </row>
-    <row r="315" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX314" s="1"/>
+    </row>
+    <row r="315" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="C315" s="1"/>
@@ -18898,8 +19411,9 @@
       <c r="AU315" s="1"/>
       <c r="AV315" s="1"/>
       <c r="AW315" s="1"/>
-    </row>
-    <row r="316" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX315" s="1"/>
+    </row>
+    <row r="316" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="C316" s="1"/>
@@ -18949,8 +19463,9 @@
       <c r="AU316" s="1"/>
       <c r="AV316" s="1"/>
       <c r="AW316" s="1"/>
-    </row>
-    <row r="317" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX316" s="1"/>
+    </row>
+    <row r="317" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="C317" s="1"/>
@@ -19000,8 +19515,9 @@
       <c r="AU317" s="1"/>
       <c r="AV317" s="1"/>
       <c r="AW317" s="1"/>
-    </row>
-    <row r="318" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX317" s="1"/>
+    </row>
+    <row r="318" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="C318" s="1"/>
@@ -19051,8 +19567,9 @@
       <c r="AU318" s="1"/>
       <c r="AV318" s="1"/>
       <c r="AW318" s="1"/>
-    </row>
-    <row r="319" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX318" s="1"/>
+    </row>
+    <row r="319" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="C319" s="1"/>
@@ -19102,8 +19619,9 @@
       <c r="AU319" s="1"/>
       <c r="AV319" s="1"/>
       <c r="AW319" s="1"/>
-    </row>
-    <row r="320" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX319" s="1"/>
+    </row>
+    <row r="320" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="C320" s="1"/>
@@ -19153,8 +19671,9 @@
       <c r="AU320" s="1"/>
       <c r="AV320" s="1"/>
       <c r="AW320" s="1"/>
-    </row>
-    <row r="321" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX320" s="1"/>
+    </row>
+    <row r="321" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="C321" s="1"/>
@@ -19204,8 +19723,9 @@
       <c r="AU321" s="1"/>
       <c r="AV321" s="1"/>
       <c r="AW321" s="1"/>
-    </row>
-    <row r="322" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX321" s="1"/>
+    </row>
+    <row r="322" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="C322" s="1"/>
@@ -19255,8 +19775,9 @@
       <c r="AU322" s="1"/>
       <c r="AV322" s="1"/>
       <c r="AW322" s="1"/>
-    </row>
-    <row r="323" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX322" s="1"/>
+    </row>
+    <row r="323" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="C323" s="1"/>
@@ -19306,8 +19827,9 @@
       <c r="AU323" s="1"/>
       <c r="AV323" s="1"/>
       <c r="AW323" s="1"/>
-    </row>
-    <row r="324" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX323" s="1"/>
+    </row>
+    <row r="324" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="C324" s="1"/>
@@ -19357,8 +19879,9 @@
       <c r="AU324" s="1"/>
       <c r="AV324" s="1"/>
       <c r="AW324" s="1"/>
-    </row>
-    <row r="325" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX324" s="1"/>
+    </row>
+    <row r="325" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="C325" s="1"/>
@@ -19408,8 +19931,9 @@
       <c r="AU325" s="1"/>
       <c r="AV325" s="1"/>
       <c r="AW325" s="1"/>
-    </row>
-    <row r="326" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX325" s="1"/>
+    </row>
+    <row r="326" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="C326" s="1"/>
@@ -19459,8 +19983,9 @@
       <c r="AU326" s="1"/>
       <c r="AV326" s="1"/>
       <c r="AW326" s="1"/>
-    </row>
-    <row r="327" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX326" s="1"/>
+    </row>
+    <row r="327" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="C327" s="1"/>
@@ -19510,8 +20035,9 @@
       <c r="AU327" s="1"/>
       <c r="AV327" s="1"/>
       <c r="AW327" s="1"/>
-    </row>
-    <row r="328" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX327" s="1"/>
+    </row>
+    <row r="328" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="C328" s="1"/>
@@ -19561,8 +20087,9 @@
       <c r="AU328" s="1"/>
       <c r="AV328" s="1"/>
       <c r="AW328" s="1"/>
-    </row>
-    <row r="329" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX328" s="1"/>
+    </row>
+    <row r="329" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="C329" s="1"/>
@@ -19612,8 +20139,9 @@
       <c r="AU329" s="1"/>
       <c r="AV329" s="1"/>
       <c r="AW329" s="1"/>
-    </row>
-    <row r="330" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX329" s="1"/>
+    </row>
+    <row r="330" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="C330" s="1"/>
@@ -19663,8 +20191,9 @@
       <c r="AU330" s="1"/>
       <c r="AV330" s="1"/>
       <c r="AW330" s="1"/>
-    </row>
-    <row r="331" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX330" s="1"/>
+    </row>
+    <row r="331" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="C331" s="1"/>
@@ -19714,8 +20243,9 @@
       <c r="AU331" s="1"/>
       <c r="AV331" s="1"/>
       <c r="AW331" s="1"/>
-    </row>
-    <row r="332" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX331" s="1"/>
+    </row>
+    <row r="332" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="C332" s="1"/>
@@ -19765,8 +20295,9 @@
       <c r="AU332" s="1"/>
       <c r="AV332" s="1"/>
       <c r="AW332" s="1"/>
-    </row>
-    <row r="333" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX332" s="1"/>
+    </row>
+    <row r="333" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="C333" s="1"/>
@@ -19816,8 +20347,9 @@
       <c r="AU333" s="1"/>
       <c r="AV333" s="1"/>
       <c r="AW333" s="1"/>
-    </row>
-    <row r="334" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX333" s="1"/>
+    </row>
+    <row r="334" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="C334" s="1"/>
@@ -19867,8 +20399,9 @@
       <c r="AU334" s="1"/>
       <c r="AV334" s="1"/>
       <c r="AW334" s="1"/>
-    </row>
-    <row r="335" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX334" s="1"/>
+    </row>
+    <row r="335" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="C335" s="1"/>
@@ -19918,8 +20451,9 @@
       <c r="AU335" s="1"/>
       <c r="AV335" s="1"/>
       <c r="AW335" s="1"/>
-    </row>
-    <row r="336" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX335" s="1"/>
+    </row>
+    <row r="336" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="C336" s="1"/>
@@ -19969,8 +20503,9 @@
       <c r="AU336" s="1"/>
       <c r="AV336" s="1"/>
       <c r="AW336" s="1"/>
-    </row>
-    <row r="337" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX336" s="1"/>
+    </row>
+    <row r="337" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="C337" s="1"/>
@@ -20020,8 +20555,9 @@
       <c r="AU337" s="1"/>
       <c r="AV337" s="1"/>
       <c r="AW337" s="1"/>
-    </row>
-    <row r="338" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX337" s="1"/>
+    </row>
+    <row r="338" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="C338" s="1"/>
@@ -20071,8 +20607,9 @@
       <c r="AU338" s="1"/>
       <c r="AV338" s="1"/>
       <c r="AW338" s="1"/>
-    </row>
-    <row r="339" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX338" s="1"/>
+    </row>
+    <row r="339" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="C339" s="1"/>
@@ -20122,8 +20659,9 @@
       <c r="AU339" s="1"/>
       <c r="AV339" s="1"/>
       <c r="AW339" s="1"/>
-    </row>
-    <row r="340" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX339" s="1"/>
+    </row>
+    <row r="340" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="C340" s="1"/>
@@ -20173,8 +20711,9 @@
       <c r="AU340" s="1"/>
       <c r="AV340" s="1"/>
       <c r="AW340" s="1"/>
-    </row>
-    <row r="341" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX340" s="1"/>
+    </row>
+    <row r="341" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="C341" s="1"/>
@@ -20224,8 +20763,9 @@
       <c r="AU341" s="1"/>
       <c r="AV341" s="1"/>
       <c r="AW341" s="1"/>
-    </row>
-    <row r="342" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX341" s="1"/>
+    </row>
+    <row r="342" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="C342" s="1"/>
@@ -20275,8 +20815,9 @@
       <c r="AU342" s="1"/>
       <c r="AV342" s="1"/>
       <c r="AW342" s="1"/>
-    </row>
-    <row r="343" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX342" s="1"/>
+    </row>
+    <row r="343" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="C343" s="1"/>
@@ -20326,8 +20867,9 @@
       <c r="AU343" s="1"/>
       <c r="AV343" s="1"/>
       <c r="AW343" s="1"/>
-    </row>
-    <row r="344" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX343" s="1"/>
+    </row>
+    <row r="344" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="C344" s="1"/>
@@ -20377,8 +20919,9 @@
       <c r="AU344" s="1"/>
       <c r="AV344" s="1"/>
       <c r="AW344" s="1"/>
-    </row>
-    <row r="345" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX344" s="1"/>
+    </row>
+    <row r="345" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="C345" s="1"/>
@@ -20428,8 +20971,9 @@
       <c r="AU345" s="1"/>
       <c r="AV345" s="1"/>
       <c r="AW345" s="1"/>
-    </row>
-    <row r="346" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX345" s="1"/>
+    </row>
+    <row r="346" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="C346" s="1"/>
@@ -20479,8 +21023,9 @@
       <c r="AU346" s="1"/>
       <c r="AV346" s="1"/>
       <c r="AW346" s="1"/>
-    </row>
-    <row r="347" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX346" s="1"/>
+    </row>
+    <row r="347" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="C347" s="1"/>
@@ -20530,8 +21075,9 @@
       <c r="AU347" s="1"/>
       <c r="AV347" s="1"/>
       <c r="AW347" s="1"/>
-    </row>
-    <row r="348" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX347" s="1"/>
+    </row>
+    <row r="348" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="C348" s="1"/>
@@ -20581,8 +21127,9 @@
       <c r="AU348" s="1"/>
       <c r="AV348" s="1"/>
       <c r="AW348" s="1"/>
-    </row>
-    <row r="349" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX348" s="1"/>
+    </row>
+    <row r="349" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="C349" s="1"/>
@@ -20632,8 +21179,9 @@
       <c r="AU349" s="1"/>
       <c r="AV349" s="1"/>
       <c r="AW349" s="1"/>
-    </row>
-    <row r="350" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX349" s="1"/>
+    </row>
+    <row r="350" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="C350" s="1"/>
@@ -20683,8 +21231,9 @@
       <c r="AU350" s="1"/>
       <c r="AV350" s="1"/>
       <c r="AW350" s="1"/>
-    </row>
-    <row r="351" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX350" s="1"/>
+    </row>
+    <row r="351" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="C351" s="1"/>
@@ -20734,8 +21283,9 @@
       <c r="AU351" s="1"/>
       <c r="AV351" s="1"/>
       <c r="AW351" s="1"/>
-    </row>
-    <row r="352" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX351" s="1"/>
+    </row>
+    <row r="352" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="C352" s="1"/>
@@ -20785,8 +21335,9 @@
       <c r="AU352" s="1"/>
       <c r="AV352" s="1"/>
       <c r="AW352" s="1"/>
-    </row>
-    <row r="353" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX352" s="1"/>
+    </row>
+    <row r="353" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="C353" s="1"/>
@@ -20836,8 +21387,9 @@
       <c r="AU353" s="1"/>
       <c r="AV353" s="1"/>
       <c r="AW353" s="1"/>
-    </row>
-    <row r="354" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX353" s="1"/>
+    </row>
+    <row r="354" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="C354" s="1"/>
@@ -20887,8 +21439,9 @@
       <c r="AU354" s="1"/>
       <c r="AV354" s="1"/>
       <c r="AW354" s="1"/>
-    </row>
-    <row r="355" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX354" s="1"/>
+    </row>
+    <row r="355" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="C355" s="1"/>
@@ -20938,8 +21491,9 @@
       <c r="AU355" s="1"/>
       <c r="AV355" s="1"/>
       <c r="AW355" s="1"/>
-    </row>
-    <row r="356" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX355" s="1"/>
+    </row>
+    <row r="356" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="C356" s="1"/>
@@ -20989,8 +21543,9 @@
       <c r="AU356" s="1"/>
       <c r="AV356" s="1"/>
       <c r="AW356" s="1"/>
-    </row>
-    <row r="357" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX356" s="1"/>
+    </row>
+    <row r="357" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="C357" s="1"/>
@@ -21040,8 +21595,9 @@
       <c r="AU357" s="1"/>
       <c r="AV357" s="1"/>
       <c r="AW357" s="1"/>
-    </row>
-    <row r="358" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX357" s="1"/>
+    </row>
+    <row r="358" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="C358" s="1"/>
@@ -21091,8 +21647,9 @@
       <c r="AU358" s="1"/>
       <c r="AV358" s="1"/>
       <c r="AW358" s="1"/>
-    </row>
-    <row r="359" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX358" s="1"/>
+    </row>
+    <row r="359" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="C359" s="1"/>
@@ -21142,8 +21699,9 @@
       <c r="AU359" s="1"/>
       <c r="AV359" s="1"/>
       <c r="AW359" s="1"/>
-    </row>
-    <row r="360" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX359" s="1"/>
+    </row>
+    <row r="360" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="C360" s="1"/>
@@ -21193,8 +21751,9 @@
       <c r="AU360" s="1"/>
       <c r="AV360" s="1"/>
       <c r="AW360" s="1"/>
-    </row>
-    <row r="361" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX360" s="1"/>
+    </row>
+    <row r="361" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="C361" s="1"/>
@@ -21244,8 +21803,9 @@
       <c r="AU361" s="1"/>
       <c r="AV361" s="1"/>
       <c r="AW361" s="1"/>
-    </row>
-    <row r="362" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX361" s="1"/>
+    </row>
+    <row r="362" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="C362" s="1"/>
@@ -21295,8 +21855,9 @@
       <c r="AU362" s="1"/>
       <c r="AV362" s="1"/>
       <c r="AW362" s="1"/>
-    </row>
-    <row r="363" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX362" s="1"/>
+    </row>
+    <row r="363" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="C363" s="1"/>
@@ -21346,8 +21907,9 @@
       <c r="AU363" s="1"/>
       <c r="AV363" s="1"/>
       <c r="AW363" s="1"/>
-    </row>
-    <row r="364" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX363" s="1"/>
+    </row>
+    <row r="364" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="C364" s="1"/>
@@ -21397,8 +21959,9 @@
       <c r="AU364" s="1"/>
       <c r="AV364" s="1"/>
       <c r="AW364" s="1"/>
-    </row>
-    <row r="365" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX364" s="1"/>
+    </row>
+    <row r="365" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="C365" s="1"/>
@@ -21448,8 +22011,9 @@
       <c r="AU365" s="1"/>
       <c r="AV365" s="1"/>
       <c r="AW365" s="1"/>
-    </row>
-    <row r="366" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX365" s="1"/>
+    </row>
+    <row r="366" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="C366" s="1"/>
@@ -21499,8 +22063,9 @@
       <c r="AU366" s="1"/>
       <c r="AV366" s="1"/>
       <c r="AW366" s="1"/>
-    </row>
-    <row r="367" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX366" s="1"/>
+    </row>
+    <row r="367" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="C367" s="1"/>
@@ -21550,8 +22115,9 @@
       <c r="AU367" s="1"/>
       <c r="AV367" s="1"/>
       <c r="AW367" s="1"/>
-    </row>
-    <row r="368" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX367" s="1"/>
+    </row>
+    <row r="368" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="C368" s="1"/>
@@ -21601,8 +22167,9 @@
       <c r="AU368" s="1"/>
       <c r="AV368" s="1"/>
       <c r="AW368" s="1"/>
-    </row>
-    <row r="369" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX368" s="1"/>
+    </row>
+    <row r="369" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="C369" s="1"/>
@@ -21652,8 +22219,9 @@
       <c r="AU369" s="1"/>
       <c r="AV369" s="1"/>
       <c r="AW369" s="1"/>
-    </row>
-    <row r="370" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX369" s="1"/>
+    </row>
+    <row r="370" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="C370" s="1"/>
@@ -21703,8 +22271,9 @@
       <c r="AU370" s="1"/>
       <c r="AV370" s="1"/>
       <c r="AW370" s="1"/>
-    </row>
-    <row r="371" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX370" s="1"/>
+    </row>
+    <row r="371" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="C371" s="1"/>
@@ -21754,8 +22323,9 @@
       <c r="AU371" s="1"/>
       <c r="AV371" s="1"/>
       <c r="AW371" s="1"/>
-    </row>
-    <row r="372" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX371" s="1"/>
+    </row>
+    <row r="372" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="C372" s="1"/>
@@ -21805,8 +22375,9 @@
       <c r="AU372" s="1"/>
       <c r="AV372" s="1"/>
       <c r="AW372" s="1"/>
-    </row>
-    <row r="373" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX372" s="1"/>
+    </row>
+    <row r="373" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="C373" s="1"/>
@@ -21856,8 +22427,9 @@
       <c r="AU373" s="1"/>
       <c r="AV373" s="1"/>
       <c r="AW373" s="1"/>
-    </row>
-    <row r="374" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX373" s="1"/>
+    </row>
+    <row r="374" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="C374" s="1"/>
@@ -21907,8 +22479,9 @@
       <c r="AU374" s="1"/>
       <c r="AV374" s="1"/>
       <c r="AW374" s="1"/>
-    </row>
-    <row r="375" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX374" s="1"/>
+    </row>
+    <row r="375" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="C375" s="1"/>
@@ -21958,8 +22531,9 @@
       <c r="AU375" s="1"/>
       <c r="AV375" s="1"/>
       <c r="AW375" s="1"/>
-    </row>
-    <row r="376" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX375" s="1"/>
+    </row>
+    <row r="376" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="C376" s="1"/>
@@ -22009,8 +22583,9 @@
       <c r="AU376" s="1"/>
       <c r="AV376" s="1"/>
       <c r="AW376" s="1"/>
-    </row>
-    <row r="377" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX376" s="1"/>
+    </row>
+    <row r="377" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="C377" s="1"/>
@@ -22060,8 +22635,9 @@
       <c r="AU377" s="1"/>
       <c r="AV377" s="1"/>
       <c r="AW377" s="1"/>
-    </row>
-    <row r="378" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX377" s="1"/>
+    </row>
+    <row r="378" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="C378" s="1"/>
@@ -22111,8 +22687,9 @@
       <c r="AU378" s="1"/>
       <c r="AV378" s="1"/>
       <c r="AW378" s="1"/>
-    </row>
-    <row r="379" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX378" s="1"/>
+    </row>
+    <row r="379" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="C379" s="1"/>
@@ -22162,8 +22739,9 @@
       <c r="AU379" s="1"/>
       <c r="AV379" s="1"/>
       <c r="AW379" s="1"/>
-    </row>
-    <row r="380" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX379" s="1"/>
+    </row>
+    <row r="380" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="C380" s="1"/>
@@ -22213,8 +22791,9 @@
       <c r="AU380" s="1"/>
       <c r="AV380" s="1"/>
       <c r="AW380" s="1"/>
-    </row>
-    <row r="381" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX380" s="1"/>
+    </row>
+    <row r="381" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="C381" s="1"/>
@@ -22264,8 +22843,9 @@
       <c r="AU381" s="1"/>
       <c r="AV381" s="1"/>
       <c r="AW381" s="1"/>
-    </row>
-    <row r="382" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX381" s="1"/>
+    </row>
+    <row r="382" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="C382" s="1"/>
@@ -22315,8 +22895,9 @@
       <c r="AU382" s="1"/>
       <c r="AV382" s="1"/>
       <c r="AW382" s="1"/>
-    </row>
-    <row r="383" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX382" s="1"/>
+    </row>
+    <row r="383" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="C383" s="1"/>
@@ -22366,8 +22947,9 @@
       <c r="AU383" s="1"/>
       <c r="AV383" s="1"/>
       <c r="AW383" s="1"/>
-    </row>
-    <row r="384" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX383" s="1"/>
+    </row>
+    <row r="384" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="C384" s="1"/>
@@ -22417,8 +22999,9 @@
       <c r="AU384" s="1"/>
       <c r="AV384" s="1"/>
       <c r="AW384" s="1"/>
-    </row>
-    <row r="385" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX384" s="1"/>
+    </row>
+    <row r="385" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="C385" s="1"/>
@@ -22468,8 +23051,9 @@
       <c r="AU385" s="1"/>
       <c r="AV385" s="1"/>
       <c r="AW385" s="1"/>
-    </row>
-    <row r="386" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX385" s="1"/>
+    </row>
+    <row r="386" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="C386" s="1"/>
@@ -22519,8 +23103,9 @@
       <c r="AU386" s="1"/>
       <c r="AV386" s="1"/>
       <c r="AW386" s="1"/>
-    </row>
-    <row r="387" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX386" s="1"/>
+    </row>
+    <row r="387" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="C387" s="1"/>
@@ -22570,8 +23155,9 @@
       <c r="AU387" s="1"/>
       <c r="AV387" s="1"/>
       <c r="AW387" s="1"/>
-    </row>
-    <row r="388" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX387" s="1"/>
+    </row>
+    <row r="388" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="C388" s="1"/>
@@ -22621,8 +23207,9 @@
       <c r="AU388" s="1"/>
       <c r="AV388" s="1"/>
       <c r="AW388" s="1"/>
-    </row>
-    <row r="389" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX388" s="1"/>
+    </row>
+    <row r="389" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="C389" s="1"/>
@@ -22672,8 +23259,9 @@
       <c r="AU389" s="1"/>
       <c r="AV389" s="1"/>
       <c r="AW389" s="1"/>
-    </row>
-    <row r="390" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX389" s="1"/>
+    </row>
+    <row r="390" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="C390" s="1"/>
@@ -22723,8 +23311,9 @@
       <c r="AU390" s="1"/>
       <c r="AV390" s="1"/>
       <c r="AW390" s="1"/>
-    </row>
-    <row r="391" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX390" s="1"/>
+    </row>
+    <row r="391" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="C391" s="1"/>
@@ -22774,8 +23363,9 @@
       <c r="AU391" s="1"/>
       <c r="AV391" s="1"/>
       <c r="AW391" s="1"/>
-    </row>
-    <row r="392" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX391" s="1"/>
+    </row>
+    <row r="392" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="C392" s="1"/>
@@ -22825,8 +23415,9 @@
       <c r="AU392" s="1"/>
       <c r="AV392" s="1"/>
       <c r="AW392" s="1"/>
-    </row>
-    <row r="393" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX392" s="1"/>
+    </row>
+    <row r="393" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="C393" s="1"/>
@@ -22876,8 +23467,9 @@
       <c r="AU393" s="1"/>
       <c r="AV393" s="1"/>
       <c r="AW393" s="1"/>
-    </row>
-    <row r="394" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX393" s="1"/>
+    </row>
+    <row r="394" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="C394" s="1"/>
@@ -22927,8 +23519,9 @@
       <c r="AU394" s="1"/>
       <c r="AV394" s="1"/>
       <c r="AW394" s="1"/>
-    </row>
-    <row r="395" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX394" s="1"/>
+    </row>
+    <row r="395" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="C395" s="1"/>
@@ -22978,8 +23571,9 @@
       <c r="AU395" s="1"/>
       <c r="AV395" s="1"/>
       <c r="AW395" s="1"/>
-    </row>
-    <row r="396" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX395" s="1"/>
+    </row>
+    <row r="396" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="C396" s="1"/>
@@ -23029,8 +23623,9 @@
       <c r="AU396" s="1"/>
       <c r="AV396" s="1"/>
       <c r="AW396" s="1"/>
-    </row>
-    <row r="397" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX396" s="1"/>
+    </row>
+    <row r="397" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="C397" s="1"/>
@@ -23080,8 +23675,9 @@
       <c r="AU397" s="1"/>
       <c r="AV397" s="1"/>
       <c r="AW397" s="1"/>
-    </row>
-    <row r="398" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX397" s="1"/>
+    </row>
+    <row r="398" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="C398" s="1"/>
@@ -23131,8 +23727,9 @@
       <c r="AU398" s="1"/>
       <c r="AV398" s="1"/>
       <c r="AW398" s="1"/>
-    </row>
-    <row r="399" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX398" s="1"/>
+    </row>
+    <row r="399" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="C399" s="1"/>
@@ -23182,8 +23779,9 @@
       <c r="AU399" s="1"/>
       <c r="AV399" s="1"/>
       <c r="AW399" s="1"/>
-    </row>
-    <row r="400" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX399" s="1"/>
+    </row>
+    <row r="400" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="C400" s="1"/>
@@ -23233,8 +23831,9 @@
       <c r="AU400" s="1"/>
       <c r="AV400" s="1"/>
       <c r="AW400" s="1"/>
-    </row>
-    <row r="401" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX400" s="1"/>
+    </row>
+    <row r="401" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="C401" s="1"/>
@@ -23284,8 +23883,9 @@
       <c r="AU401" s="1"/>
       <c r="AV401" s="1"/>
       <c r="AW401" s="1"/>
-    </row>
-    <row r="402" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX401" s="1"/>
+    </row>
+    <row r="402" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="C402" s="1"/>
@@ -23335,8 +23935,9 @@
       <c r="AU402" s="1"/>
       <c r="AV402" s="1"/>
       <c r="AW402" s="1"/>
-    </row>
-    <row r="403" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX402" s="1"/>
+    </row>
+    <row r="403" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="C403" s="1"/>
@@ -23386,8 +23987,9 @@
       <c r="AU403" s="1"/>
       <c r="AV403" s="1"/>
       <c r="AW403" s="1"/>
-    </row>
-    <row r="404" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX403" s="1"/>
+    </row>
+    <row r="404" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="C404" s="1"/>
@@ -23437,8 +24039,9 @@
       <c r="AU404" s="1"/>
       <c r="AV404" s="1"/>
       <c r="AW404" s="1"/>
-    </row>
-    <row r="405" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX404" s="1"/>
+    </row>
+    <row r="405" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="C405" s="1"/>
@@ -23488,8 +24091,9 @@
       <c r="AU405" s="1"/>
       <c r="AV405" s="1"/>
       <c r="AW405" s="1"/>
-    </row>
-    <row r="406" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX405" s="1"/>
+    </row>
+    <row r="406" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="C406" s="1"/>
@@ -23539,8 +24143,9 @@
       <c r="AU406" s="1"/>
       <c r="AV406" s="1"/>
       <c r="AW406" s="1"/>
-    </row>
-    <row r="407" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX406" s="1"/>
+    </row>
+    <row r="407" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="C407" s="1"/>
@@ -23590,8 +24195,9 @@
       <c r="AU407" s="1"/>
       <c r="AV407" s="1"/>
       <c r="AW407" s="1"/>
-    </row>
-    <row r="408" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX407" s="1"/>
+    </row>
+    <row r="408" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="C408" s="1"/>
@@ -23641,8 +24247,9 @@
       <c r="AU408" s="1"/>
       <c r="AV408" s="1"/>
       <c r="AW408" s="1"/>
-    </row>
-    <row r="409" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX408" s="1"/>
+    </row>
+    <row r="409" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="C409" s="1"/>
@@ -23692,8 +24299,9 @@
       <c r="AU409" s="1"/>
       <c r="AV409" s="1"/>
       <c r="AW409" s="1"/>
-    </row>
-    <row r="410" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX409" s="1"/>
+    </row>
+    <row r="410" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="C410" s="1"/>
@@ -23743,8 +24351,9 @@
       <c r="AU410" s="1"/>
       <c r="AV410" s="1"/>
       <c r="AW410" s="1"/>
-    </row>
-    <row r="411" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX410" s="1"/>
+    </row>
+    <row r="411" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="C411" s="1"/>
@@ -23794,8 +24403,9 @@
       <c r="AU411" s="1"/>
       <c r="AV411" s="1"/>
       <c r="AW411" s="1"/>
-    </row>
-    <row r="412" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX411" s="1"/>
+    </row>
+    <row r="412" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="C412" s="1"/>
@@ -23845,8 +24455,9 @@
       <c r="AU412" s="1"/>
       <c r="AV412" s="1"/>
       <c r="AW412" s="1"/>
-    </row>
-    <row r="413" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX412" s="1"/>
+    </row>
+    <row r="413" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="C413" s="1"/>
@@ -23896,8 +24507,9 @@
       <c r="AU413" s="1"/>
       <c r="AV413" s="1"/>
       <c r="AW413" s="1"/>
-    </row>
-    <row r="414" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX413" s="1"/>
+    </row>
+    <row r="414" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="C414" s="1"/>
@@ -23947,8 +24559,9 @@
       <c r="AU414" s="1"/>
       <c r="AV414" s="1"/>
       <c r="AW414" s="1"/>
-    </row>
-    <row r="415" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX414" s="1"/>
+    </row>
+    <row r="415" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="C415" s="1"/>
@@ -23998,8 +24611,9 @@
       <c r="AU415" s="1"/>
       <c r="AV415" s="1"/>
       <c r="AW415" s="1"/>
-    </row>
-    <row r="416" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX415" s="1"/>
+    </row>
+    <row r="416" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="C416" s="1"/>
@@ -24049,8 +24663,9 @@
       <c r="AU416" s="1"/>
       <c r="AV416" s="1"/>
       <c r="AW416" s="1"/>
-    </row>
-    <row r="417" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX416" s="1"/>
+    </row>
+    <row r="417" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="C417" s="1"/>
@@ -24100,8 +24715,9 @@
       <c r="AU417" s="1"/>
       <c r="AV417" s="1"/>
       <c r="AW417" s="1"/>
-    </row>
-    <row r="418" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX417" s="1"/>
+    </row>
+    <row r="418" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="C418" s="1"/>
@@ -24151,8 +24767,9 @@
       <c r="AU418" s="1"/>
       <c r="AV418" s="1"/>
       <c r="AW418" s="1"/>
-    </row>
-    <row r="419" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX418" s="1"/>
+    </row>
+    <row r="419" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="C419" s="1"/>
@@ -24202,8 +24819,9 @@
       <c r="AU419" s="1"/>
       <c r="AV419" s="1"/>
       <c r="AW419" s="1"/>
-    </row>
-    <row r="420" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX419" s="1"/>
+    </row>
+    <row r="420" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="C420" s="1"/>
@@ -24253,8 +24871,9 @@
       <c r="AU420" s="1"/>
       <c r="AV420" s="1"/>
       <c r="AW420" s="1"/>
-    </row>
-    <row r="421" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX420" s="1"/>
+    </row>
+    <row r="421" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="C421" s="1"/>
@@ -24304,8 +24923,9 @@
       <c r="AU421" s="1"/>
       <c r="AV421" s="1"/>
       <c r="AW421" s="1"/>
-    </row>
-    <row r="422" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX421" s="1"/>
+    </row>
+    <row r="422" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="C422" s="1"/>
@@ -24355,8 +24975,9 @@
       <c r="AU422" s="1"/>
       <c r="AV422" s="1"/>
       <c r="AW422" s="1"/>
-    </row>
-    <row r="423" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX422" s="1"/>
+    </row>
+    <row r="423" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="C423" s="1"/>
@@ -24406,8 +25027,9 @@
       <c r="AU423" s="1"/>
       <c r="AV423" s="1"/>
       <c r="AW423" s="1"/>
-    </row>
-    <row r="424" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX423" s="1"/>
+    </row>
+    <row r="424" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="C424" s="1"/>
@@ -24457,8 +25079,9 @@
       <c r="AU424" s="1"/>
       <c r="AV424" s="1"/>
       <c r="AW424" s="1"/>
-    </row>
-    <row r="425" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX424" s="1"/>
+    </row>
+    <row r="425" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="C425" s="1"/>
@@ -24508,8 +25131,9 @@
       <c r="AU425" s="1"/>
       <c r="AV425" s="1"/>
       <c r="AW425" s="1"/>
-    </row>
-    <row r="426" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX425" s="1"/>
+    </row>
+    <row r="426" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="C426" s="1"/>
@@ -24559,8 +25183,9 @@
       <c r="AU426" s="1"/>
       <c r="AV426" s="1"/>
       <c r="AW426" s="1"/>
-    </row>
-    <row r="427" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX426" s="1"/>
+    </row>
+    <row r="427" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="C427" s="1"/>
@@ -24610,8 +25235,9 @@
       <c r="AU427" s="1"/>
       <c r="AV427" s="1"/>
       <c r="AW427" s="1"/>
-    </row>
-    <row r="428" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX427" s="1"/>
+    </row>
+    <row r="428" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="C428" s="1"/>
@@ -24661,8 +25287,9 @@
       <c r="AU428" s="1"/>
       <c r="AV428" s="1"/>
       <c r="AW428" s="1"/>
-    </row>
-    <row r="429" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX428" s="1"/>
+    </row>
+    <row r="429" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="C429" s="1"/>
@@ -24712,8 +25339,9 @@
       <c r="AU429" s="1"/>
       <c r="AV429" s="1"/>
       <c r="AW429" s="1"/>
-    </row>
-    <row r="430" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX429" s="1"/>
+    </row>
+    <row r="430" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="C430" s="1"/>
@@ -24763,8 +25391,9 @@
       <c r="AU430" s="1"/>
       <c r="AV430" s="1"/>
       <c r="AW430" s="1"/>
-    </row>
-    <row r="431" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX430" s="1"/>
+    </row>
+    <row r="431" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="C431" s="1"/>
@@ -24814,8 +25443,9 @@
       <c r="AU431" s="1"/>
       <c r="AV431" s="1"/>
       <c r="AW431" s="1"/>
-    </row>
-    <row r="432" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX431" s="1"/>
+    </row>
+    <row r="432" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="C432" s="1"/>
@@ -24865,8 +25495,9 @@
       <c r="AU432" s="1"/>
       <c r="AV432" s="1"/>
       <c r="AW432" s="1"/>
-    </row>
-    <row r="433" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX432" s="1"/>
+    </row>
+    <row r="433" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="C433" s="1"/>
@@ -24916,8 +25547,9 @@
       <c r="AU433" s="1"/>
       <c r="AV433" s="1"/>
       <c r="AW433" s="1"/>
-    </row>
-    <row r="434" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX433" s="1"/>
+    </row>
+    <row r="434" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="C434" s="1"/>
@@ -24967,8 +25599,9 @@
       <c r="AU434" s="1"/>
       <c r="AV434" s="1"/>
       <c r="AW434" s="1"/>
-    </row>
-    <row r="435" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX434" s="1"/>
+    </row>
+    <row r="435" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="C435" s="1"/>
@@ -25018,8 +25651,9 @@
       <c r="AU435" s="1"/>
       <c r="AV435" s="1"/>
       <c r="AW435" s="1"/>
-    </row>
-    <row r="436" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX435" s="1"/>
+    </row>
+    <row r="436" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="C436" s="1"/>
@@ -25069,8 +25703,9 @@
       <c r="AU436" s="1"/>
       <c r="AV436" s="1"/>
       <c r="AW436" s="1"/>
-    </row>
-    <row r="437" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX436" s="1"/>
+    </row>
+    <row r="437" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="C437" s="1"/>
@@ -25120,8 +25755,9 @@
       <c r="AU437" s="1"/>
       <c r="AV437" s="1"/>
       <c r="AW437" s="1"/>
-    </row>
-    <row r="438" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX437" s="1"/>
+    </row>
+    <row r="438" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="C438" s="1"/>
@@ -25171,8 +25807,9 @@
       <c r="AU438" s="1"/>
       <c r="AV438" s="1"/>
       <c r="AW438" s="1"/>
-    </row>
-    <row r="439" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX438" s="1"/>
+    </row>
+    <row r="439" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="C439" s="1"/>
@@ -25222,8 +25859,9 @@
       <c r="AU439" s="1"/>
       <c r="AV439" s="1"/>
       <c r="AW439" s="1"/>
-    </row>
-    <row r="440" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX439" s="1"/>
+    </row>
+    <row r="440" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="C440" s="1"/>
@@ -25273,8 +25911,9 @@
       <c r="AU440" s="1"/>
       <c r="AV440" s="1"/>
       <c r="AW440" s="1"/>
-    </row>
-    <row r="441" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX440" s="1"/>
+    </row>
+    <row r="441" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="C441" s="1"/>
@@ -25324,8 +25963,9 @@
       <c r="AU441" s="1"/>
       <c r="AV441" s="1"/>
       <c r="AW441" s="1"/>
-    </row>
-    <row r="442" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX441" s="1"/>
+    </row>
+    <row r="442" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="C442" s="1"/>
@@ -25375,8 +26015,9 @@
       <c r="AU442" s="1"/>
       <c r="AV442" s="1"/>
       <c r="AW442" s="1"/>
-    </row>
-    <row r="443" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX442" s="1"/>
+    </row>
+    <row r="443" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="C443" s="1"/>
@@ -25426,8 +26067,9 @@
       <c r="AU443" s="1"/>
       <c r="AV443" s="1"/>
       <c r="AW443" s="1"/>
-    </row>
-    <row r="444" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX443" s="1"/>
+    </row>
+    <row r="444" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="C444" s="1"/>
@@ -25477,8 +26119,9 @@
       <c r="AU444" s="1"/>
       <c r="AV444" s="1"/>
       <c r="AW444" s="1"/>
-    </row>
-    <row r="445" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX444" s="1"/>
+    </row>
+    <row r="445" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="C445" s="1"/>
@@ -25528,8 +26171,9 @@
       <c r="AU445" s="1"/>
       <c r="AV445" s="1"/>
       <c r="AW445" s="1"/>
-    </row>
-    <row r="446" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX445" s="1"/>
+    </row>
+    <row r="446" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="C446" s="1"/>
@@ -25579,8 +26223,9 @@
       <c r="AU446" s="1"/>
       <c r="AV446" s="1"/>
       <c r="AW446" s="1"/>
-    </row>
-    <row r="447" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX446" s="1"/>
+    </row>
+    <row r="447" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="C447" s="1"/>
@@ -25630,8 +26275,9 @@
       <c r="AU447" s="1"/>
       <c r="AV447" s="1"/>
       <c r="AW447" s="1"/>
-    </row>
-    <row r="448" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX447" s="1"/>
+    </row>
+    <row r="448" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="C448" s="1"/>
@@ -25681,8 +26327,9 @@
       <c r="AU448" s="1"/>
       <c r="AV448" s="1"/>
       <c r="AW448" s="1"/>
-    </row>
-    <row r="449" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX448" s="1"/>
+    </row>
+    <row r="449" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="C449" s="1"/>
@@ -25732,8 +26379,9 @@
       <c r="AU449" s="1"/>
       <c r="AV449" s="1"/>
       <c r="AW449" s="1"/>
-    </row>
-    <row r="450" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX449" s="1"/>
+    </row>
+    <row r="450" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="C450" s="1"/>
@@ -25783,8 +26431,9 @@
       <c r="AU450" s="1"/>
       <c r="AV450" s="1"/>
       <c r="AW450" s="1"/>
-    </row>
-    <row r="451" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX450" s="1"/>
+    </row>
+    <row r="451" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="C451" s="1"/>
@@ -25834,8 +26483,9 @@
       <c r="AU451" s="1"/>
       <c r="AV451" s="1"/>
       <c r="AW451" s="1"/>
-    </row>
-    <row r="452" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX451" s="1"/>
+    </row>
+    <row r="452" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="C452" s="1"/>
@@ -25885,8 +26535,9 @@
       <c r="AU452" s="1"/>
       <c r="AV452" s="1"/>
       <c r="AW452" s="1"/>
-    </row>
-    <row r="453" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX452" s="1"/>
+    </row>
+    <row r="453" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="C453" s="1"/>
@@ -25936,8 +26587,9 @@
       <c r="AU453" s="1"/>
       <c r="AV453" s="1"/>
       <c r="AW453" s="1"/>
-    </row>
-    <row r="454" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX453" s="1"/>
+    </row>
+    <row r="454" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="C454" s="1"/>
@@ -25987,8 +26639,9 @@
       <c r="AU454" s="1"/>
       <c r="AV454" s="1"/>
       <c r="AW454" s="1"/>
-    </row>
-    <row r="455" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX454" s="1"/>
+    </row>
+    <row r="455" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="C455" s="1"/>
@@ -26038,8 +26691,9 @@
       <c r="AU455" s="1"/>
       <c r="AV455" s="1"/>
       <c r="AW455" s="1"/>
-    </row>
-    <row r="456" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX455" s="1"/>
+    </row>
+    <row r="456" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="C456" s="1"/>
@@ -26089,8 +26743,9 @@
       <c r="AU456" s="1"/>
       <c r="AV456" s="1"/>
       <c r="AW456" s="1"/>
-    </row>
-    <row r="457" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX456" s="1"/>
+    </row>
+    <row r="457" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="C457" s="1"/>
@@ -26140,8 +26795,9 @@
       <c r="AU457" s="1"/>
       <c r="AV457" s="1"/>
       <c r="AW457" s="1"/>
-    </row>
-    <row r="458" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX457" s="1"/>
+    </row>
+    <row r="458" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="C458" s="1"/>
@@ -26191,8 +26847,9 @@
       <c r="AU458" s="1"/>
       <c r="AV458" s="1"/>
       <c r="AW458" s="1"/>
-    </row>
-    <row r="459" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX458" s="1"/>
+    </row>
+    <row r="459" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="C459" s="1"/>
@@ -26242,8 +26899,9 @@
       <c r="AU459" s="1"/>
       <c r="AV459" s="1"/>
       <c r="AW459" s="1"/>
-    </row>
-    <row r="460" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX459" s="1"/>
+    </row>
+    <row r="460" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="C460" s="1"/>
@@ -26293,8 +26951,9 @@
       <c r="AU460" s="1"/>
       <c r="AV460" s="1"/>
       <c r="AW460" s="1"/>
-    </row>
-    <row r="461" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX460" s="1"/>
+    </row>
+    <row r="461" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="C461" s="1"/>
@@ -26344,8 +27003,9 @@
       <c r="AU461" s="1"/>
       <c r="AV461" s="1"/>
       <c r="AW461" s="1"/>
-    </row>
-    <row r="462" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX461" s="1"/>
+    </row>
+    <row r="462" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="C462" s="1"/>
@@ -26395,8 +27055,9 @@
       <c r="AU462" s="1"/>
       <c r="AV462" s="1"/>
       <c r="AW462" s="1"/>
-    </row>
-    <row r="463" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX462" s="1"/>
+    </row>
+    <row r="463" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="C463" s="1"/>
@@ -26446,8 +27107,9 @@
       <c r="AU463" s="1"/>
       <c r="AV463" s="1"/>
       <c r="AW463" s="1"/>
-    </row>
-    <row r="464" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX463" s="1"/>
+    </row>
+    <row r="464" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="C464" s="1"/>
@@ -26497,8 +27159,9 @@
       <c r="AU464" s="1"/>
       <c r="AV464" s="1"/>
       <c r="AW464" s="1"/>
-    </row>
-    <row r="465" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX464" s="1"/>
+    </row>
+    <row r="465" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="C465" s="1"/>
@@ -26548,8 +27211,9 @@
       <c r="AU465" s="1"/>
       <c r="AV465" s="1"/>
       <c r="AW465" s="1"/>
-    </row>
-    <row r="466" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX465" s="1"/>
+    </row>
+    <row r="466" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="C466" s="1"/>
@@ -26599,8 +27263,9 @@
       <c r="AU466" s="1"/>
       <c r="AV466" s="1"/>
       <c r="AW466" s="1"/>
-    </row>
-    <row r="467" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX466" s="1"/>
+    </row>
+    <row r="467" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="C467" s="1"/>
@@ -26650,8 +27315,9 @@
       <c r="AU467" s="1"/>
       <c r="AV467" s="1"/>
       <c r="AW467" s="1"/>
-    </row>
-    <row r="468" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX467" s="1"/>
+    </row>
+    <row r="468" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="C468" s="1"/>
@@ -26701,8 +27367,9 @@
       <c r="AU468" s="1"/>
       <c r="AV468" s="1"/>
       <c r="AW468" s="1"/>
-    </row>
-    <row r="469" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX468" s="1"/>
+    </row>
+    <row r="469" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="C469" s="1"/>
@@ -26752,8 +27419,9 @@
       <c r="AU469" s="1"/>
       <c r="AV469" s="1"/>
       <c r="AW469" s="1"/>
-    </row>
-    <row r="470" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX469" s="1"/>
+    </row>
+    <row r="470" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="C470" s="1"/>
@@ -26803,8 +27471,9 @@
       <c r="AU470" s="1"/>
       <c r="AV470" s="1"/>
       <c r="AW470" s="1"/>
-    </row>
-    <row r="471" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX470" s="1"/>
+    </row>
+    <row r="471" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="C471" s="1"/>
@@ -26854,8 +27523,9 @@
       <c r="AU471" s="1"/>
       <c r="AV471" s="1"/>
       <c r="AW471" s="1"/>
-    </row>
-    <row r="472" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX471" s="1"/>
+    </row>
+    <row r="472" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="C472" s="1"/>
@@ -26905,8 +27575,9 @@
       <c r="AU472" s="1"/>
       <c r="AV472" s="1"/>
       <c r="AW472" s="1"/>
-    </row>
-    <row r="473" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX472" s="1"/>
+    </row>
+    <row r="473" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="C473" s="1"/>
@@ -26956,8 +27627,9 @@
       <c r="AU473" s="1"/>
       <c r="AV473" s="1"/>
       <c r="AW473" s="1"/>
-    </row>
-    <row r="474" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX473" s="1"/>
+    </row>
+    <row r="474" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="C474" s="1"/>
@@ -27007,8 +27679,9 @@
       <c r="AU474" s="1"/>
       <c r="AV474" s="1"/>
       <c r="AW474" s="1"/>
-    </row>
-    <row r="475" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX474" s="1"/>
+    </row>
+    <row r="475" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="C475" s="1"/>
@@ -27058,8 +27731,9 @@
       <c r="AU475" s="1"/>
       <c r="AV475" s="1"/>
       <c r="AW475" s="1"/>
-    </row>
-    <row r="476" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX475" s="1"/>
+    </row>
+    <row r="476" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="C476" s="1"/>
@@ -27109,8 +27783,9 @@
       <c r="AU476" s="1"/>
       <c r="AV476" s="1"/>
       <c r="AW476" s="1"/>
-    </row>
-    <row r="477" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX476" s="1"/>
+    </row>
+    <row r="477" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="C477" s="1"/>
@@ -27160,8 +27835,9 @@
       <c r="AU477" s="1"/>
       <c r="AV477" s="1"/>
       <c r="AW477" s="1"/>
-    </row>
-    <row r="478" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX477" s="1"/>
+    </row>
+    <row r="478" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="C478" s="1"/>
@@ -27211,8 +27887,9 @@
       <c r="AU478" s="1"/>
       <c r="AV478" s="1"/>
       <c r="AW478" s="1"/>
-    </row>
-    <row r="479" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX478" s="1"/>
+    </row>
+    <row r="479" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="C479" s="1"/>
@@ -27262,8 +27939,9 @@
       <c r="AU479" s="1"/>
       <c r="AV479" s="1"/>
       <c r="AW479" s="1"/>
-    </row>
-    <row r="480" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX479" s="1"/>
+    </row>
+    <row r="480" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="C480" s="1"/>
@@ -27313,8 +27991,9 @@
       <c r="AU480" s="1"/>
       <c r="AV480" s="1"/>
       <c r="AW480" s="1"/>
-    </row>
-    <row r="481" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX480" s="1"/>
+    </row>
+    <row r="481" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="C481" s="1"/>
@@ -27364,8 +28043,9 @@
       <c r="AU481" s="1"/>
       <c r="AV481" s="1"/>
       <c r="AW481" s="1"/>
-    </row>
-    <row r="482" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX481" s="1"/>
+    </row>
+    <row r="482" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="C482" s="1"/>
@@ -27415,8 +28095,9 @@
       <c r="AU482" s="1"/>
       <c r="AV482" s="1"/>
       <c r="AW482" s="1"/>
-    </row>
-    <row r="483" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX482" s="1"/>
+    </row>
+    <row r="483" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="C483" s="1"/>
@@ -27466,8 +28147,9 @@
       <c r="AU483" s="1"/>
       <c r="AV483" s="1"/>
       <c r="AW483" s="1"/>
-    </row>
-    <row r="484" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX483" s="1"/>
+    </row>
+    <row r="484" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="C484" s="1"/>
@@ -27517,8 +28199,9 @@
       <c r="AU484" s="1"/>
       <c r="AV484" s="1"/>
       <c r="AW484" s="1"/>
-    </row>
-    <row r="485" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX484" s="1"/>
+    </row>
+    <row r="485" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="C485" s="1"/>
@@ -27568,8 +28251,9 @@
       <c r="AU485" s="1"/>
       <c r="AV485" s="1"/>
       <c r="AW485" s="1"/>
-    </row>
-    <row r="486" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX485" s="1"/>
+    </row>
+    <row r="486" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="C486" s="1"/>
@@ -27619,8 +28303,9 @@
       <c r="AU486" s="1"/>
       <c r="AV486" s="1"/>
       <c r="AW486" s="1"/>
-    </row>
-    <row r="487" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX486" s="1"/>
+    </row>
+    <row r="487" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="C487" s="1"/>
@@ -27670,8 +28355,9 @@
       <c r="AU487" s="1"/>
       <c r="AV487" s="1"/>
       <c r="AW487" s="1"/>
-    </row>
-    <row r="488" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX487" s="1"/>
+    </row>
+    <row r="488" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="C488" s="1"/>
@@ -27721,8 +28407,9 @@
       <c r="AU488" s="1"/>
       <c r="AV488" s="1"/>
       <c r="AW488" s="1"/>
-    </row>
-    <row r="489" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX488" s="1"/>
+    </row>
+    <row r="489" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="C489" s="1"/>
@@ -27772,8 +28459,9 @@
       <c r="AU489" s="1"/>
       <c r="AV489" s="1"/>
       <c r="AW489" s="1"/>
-    </row>
-    <row r="490" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX489" s="1"/>
+    </row>
+    <row r="490" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="C490" s="1"/>
@@ -27823,8 +28511,9 @@
       <c r="AU490" s="1"/>
       <c r="AV490" s="1"/>
       <c r="AW490" s="1"/>
-    </row>
-    <row r="491" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX490" s="1"/>
+    </row>
+    <row r="491" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="C491" s="1"/>
@@ -27874,8 +28563,9 @@
       <c r="AU491" s="1"/>
       <c r="AV491" s="1"/>
       <c r="AW491" s="1"/>
-    </row>
-    <row r="492" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX491" s="1"/>
+    </row>
+    <row r="492" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="C492" s="1"/>
@@ -27925,8 +28615,9 @@
       <c r="AU492" s="1"/>
       <c r="AV492" s="1"/>
       <c r="AW492" s="1"/>
-    </row>
-    <row r="493" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX492" s="1"/>
+    </row>
+    <row r="493" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="C493" s="1"/>
@@ -27976,8 +28667,9 @@
       <c r="AU493" s="1"/>
       <c r="AV493" s="1"/>
       <c r="AW493" s="1"/>
-    </row>
-    <row r="494" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX493" s="1"/>
+    </row>
+    <row r="494" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="C494" s="1"/>
@@ -28027,8 +28719,9 @@
       <c r="AU494" s="1"/>
       <c r="AV494" s="1"/>
       <c r="AW494" s="1"/>
-    </row>
-    <row r="495" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX494" s="1"/>
+    </row>
+    <row r="495" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="C495" s="1"/>
@@ -28078,8 +28771,9 @@
       <c r="AU495" s="1"/>
       <c r="AV495" s="1"/>
       <c r="AW495" s="1"/>
-    </row>
-    <row r="496" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX495" s="1"/>
+    </row>
+    <row r="496" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="C496" s="1"/>
@@ -28129,8 +28823,9 @@
       <c r="AU496" s="1"/>
       <c r="AV496" s="1"/>
       <c r="AW496" s="1"/>
-    </row>
-    <row r="497" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX496" s="1"/>
+    </row>
+    <row r="497" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="C497" s="1"/>
@@ -28180,8 +28875,9 @@
       <c r="AU497" s="1"/>
       <c r="AV497" s="1"/>
       <c r="AW497" s="1"/>
-    </row>
-    <row r="498" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX497" s="1"/>
+    </row>
+    <row r="498" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="C498" s="1"/>
@@ -28231,8 +28927,9 @@
       <c r="AU498" s="1"/>
       <c r="AV498" s="1"/>
       <c r="AW498" s="1"/>
-    </row>
-    <row r="499" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AX498" s="1"/>
+    </row>
+    <row r="499" spans="1:50" x14ac:dyDescent="0.25">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="C499" s="1"/>
@@ -28282,9 +28979,100 @@
       <c r="AU499" s="1"/>
       <c r="AV499" s="1"/>
       <c r="AW499" s="1"/>
+      <c r="AX499" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:Y51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A3:Z51" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B97F4C30-AC8A-40A8-9494-FCF39EC51E99}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B3">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+      <c r="B4">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B5">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>74</v>
+      </c>
+      <c r="B10">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>